--- a/research/traditional_assets/database/data/morocco/morocco_hospitals_healthcare_facilities.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_hospitals_healthcare_facilities.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08914056895989383</v>
+        <v>0.08888591913922218</v>
       </c>
       <c r="C2">
-        <v>1565.765165305025</v>
+        <v>1559.277274919595</v>
       </c>
       <c r="D2">
-        <v>1565.765165305025</v>
+        <v>1575.019274919595</v>
       </c>
       <c r="E2">
-        <v>-104.3</v>
+        <v>-88.55800000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15.742</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1439,28 +1439,28 @@
         <v>66.024</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.7918226</v>
       </c>
       <c r="N2">
-        <v>66.024</v>
+        <v>65.2321774</v>
       </c>
       <c r="O2">
-        <v>21.12768</v>
+        <v>20.874296768</v>
       </c>
       <c r="P2">
-        <v>44.89632</v>
+        <v>44.357880632</v>
       </c>
       <c r="Q2">
-        <v>45.07232</v>
+        <v>44.533880632</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08914056895989383</v>
+        <v>0.08943826175679008</v>
       </c>
       <c r="T2">
-        <v>0.5648729042001043</v>
+        <v>0.5687528392996606</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>83.38231315953851</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08888591913922218</v>
+        <v>0.08863126931855052</v>
       </c>
       <c r="C3">
-        <v>1559.277274919595</v>
+        <v>1552.899423643036</v>
       </c>
       <c r="D3">
-        <v>1575.019274919595</v>
+        <v>1584.383423643036</v>
       </c>
       <c r="E3">
-        <v>-88.55800000000001</v>
+        <v>-72.816</v>
       </c>
       <c r="F3">
-        <v>15.742</v>
+        <v>31.484</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1521,28 +1521,28 @@
         <v>66.024</v>
       </c>
       <c r="M3">
-        <v>0.7918226</v>
+        <v>1.5836452</v>
       </c>
       <c r="N3">
-        <v>65.2321774</v>
+        <v>64.44035479999999</v>
       </c>
       <c r="O3">
-        <v>20.874296768</v>
+        <v>20.620913536</v>
       </c>
       <c r="P3">
-        <v>44.357880632</v>
+        <v>43.81944126399999</v>
       </c>
       <c r="Q3">
-        <v>44.533880632</v>
+        <v>43.99544126399999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08943826175679008</v>
+        <v>0.08974202991688829</v>
       </c>
       <c r="T3">
-        <v>0.5687528392996606</v>
+        <v>0.5727119567481873</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>83.38231315953851</v>
+        <v>41.69115657976925</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08863126931855052</v>
+        <v>0.08837661949787885</v>
       </c>
       <c r="C4">
-        <v>1552.899423643036</v>
+        <v>1546.633585899788</v>
       </c>
       <c r="D4">
-        <v>1584.383423643036</v>
+        <v>1593.859585899788</v>
       </c>
       <c r="E4">
-        <v>-72.816</v>
+        <v>-57.07400000000001</v>
       </c>
       <c r="F4">
-        <v>31.484</v>
+        <v>47.226</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1603,28 +1603,28 @@
         <v>66.024</v>
       </c>
       <c r="M4">
-        <v>1.5836452</v>
+        <v>2.3754678</v>
       </c>
       <c r="N4">
-        <v>64.44035479999999</v>
+        <v>63.6485322</v>
       </c>
       <c r="O4">
-        <v>20.620913536</v>
+        <v>20.367530304</v>
       </c>
       <c r="P4">
-        <v>43.81944126399999</v>
+        <v>43.281001896</v>
       </c>
       <c r="Q4">
-        <v>43.99544126399999</v>
+        <v>43.457001896</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08974202991688829</v>
+        <v>0.09005206133801943</v>
       </c>
       <c r="T4">
-        <v>0.5727119567481873</v>
+        <v>0.5767527054843127</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>41.69115657976925</v>
+        <v>27.79410438651283</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08837661949787885</v>
+        <v>0.08812196967720719</v>
       </c>
       <c r="C5">
-        <v>1546.633585899788</v>
+        <v>1540.48178363446</v>
       </c>
       <c r="D5">
-        <v>1593.859585899788</v>
+        <v>1603.44978363446</v>
       </c>
       <c r="E5">
-        <v>-57.07400000000001</v>
+        <v>-41.33200000000001</v>
       </c>
       <c r="F5">
-        <v>47.226</v>
+        <v>62.968</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1685,28 +1685,28 @@
         <v>66.024</v>
       </c>
       <c r="M5">
-        <v>2.3754678</v>
+        <v>3.1672904</v>
       </c>
       <c r="N5">
-        <v>63.6485322</v>
+        <v>62.8567096</v>
       </c>
       <c r="O5">
-        <v>20.367530304</v>
+        <v>20.114147072</v>
       </c>
       <c r="P5">
-        <v>43.281001896</v>
+        <v>42.742562528</v>
       </c>
       <c r="Q5">
-        <v>43.457001896</v>
+        <v>42.918562528</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09005206133801943</v>
+        <v>0.09036855174709083</v>
       </c>
       <c r="T5">
-        <v>0.5767527054843127</v>
+        <v>0.5808776364857738</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>27.79410438651283</v>
+        <v>20.84557828988463</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08812196967720719</v>
+        <v>0.08786731985653552</v>
       </c>
       <c r="C6">
-        <v>1540.48178363446</v>
+        <v>1534.446087750126</v>
       </c>
       <c r="D6">
-        <v>1603.44978363446</v>
+        <v>1613.156087750126</v>
       </c>
       <c r="E6">
-        <v>-41.33200000000001</v>
+        <v>-25.59</v>
       </c>
       <c r="F6">
-        <v>62.968</v>
+        <v>78.71000000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1767,28 +1767,28 @@
         <v>66.024</v>
       </c>
       <c r="M6">
-        <v>3.1672904</v>
+        <v>3.959113</v>
       </c>
       <c r="N6">
-        <v>62.8567096</v>
+        <v>62.064887</v>
       </c>
       <c r="O6">
-        <v>20.114147072</v>
+        <v>19.86076384</v>
       </c>
       <c r="P6">
-        <v>42.742562528</v>
+        <v>42.20412315999999</v>
       </c>
       <c r="Q6">
-        <v>42.918562528</v>
+        <v>42.38012316</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09036855174709083</v>
+        <v>0.09069170511214267</v>
       </c>
       <c r="T6">
-        <v>0.5808776364857738</v>
+        <v>0.5850894081398975</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>20.84557828988463</v>
+        <v>16.6764626319077</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08786731985653552</v>
+        <v>0.08761267003586386</v>
       </c>
       <c r="C7">
-        <v>1534.446087750126</v>
+        <v>1528.528619599171</v>
       </c>
       <c r="D7">
-        <v>1613.156087750126</v>
+        <v>1622.980619599171</v>
       </c>
       <c r="E7">
-        <v>-25.59</v>
+        <v>-9.847999999999999</v>
       </c>
       <c r="F7">
-        <v>78.71000000000001</v>
+        <v>94.45200000000001</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1849,28 +1849,28 @@
         <v>66.024</v>
       </c>
       <c r="M7">
-        <v>3.959113</v>
+        <v>4.7509356</v>
       </c>
       <c r="N7">
-        <v>62.064887</v>
+        <v>61.2730644</v>
       </c>
       <c r="O7">
-        <v>19.86076384</v>
+        <v>19.607380608</v>
       </c>
       <c r="P7">
-        <v>42.20412315999999</v>
+        <v>41.665683792</v>
       </c>
       <c r="Q7">
-        <v>42.38012316</v>
+        <v>41.841683792</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09069170511214267</v>
+        <v>0.09102173408070624</v>
       </c>
       <c r="T7">
-        <v>0.5850894081398975</v>
+        <v>0.5893907919568747</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>16.6764626319077</v>
+        <v>13.89705219325642</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08761267003586386</v>
+        <v>0.08742942021519222</v>
       </c>
       <c r="C8">
-        <v>1528.528619599171</v>
+        <v>1519.930867728444</v>
       </c>
       <c r="D8">
-        <v>1622.980619599171</v>
+        <v>1630.124867728444</v>
       </c>
       <c r="E8">
-        <v>-9.848000000000013</v>
+        <v>5.893999999999977</v>
       </c>
       <c r="F8">
-        <v>94.452</v>
+        <v>110.194</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1931,45 +1931,45 @@
         <v>66.024</v>
       </c>
       <c r="M8">
-        <v>4.7509356</v>
+        <v>5.7080492</v>
       </c>
       <c r="N8">
-        <v>61.2730644</v>
+        <v>60.3159508</v>
       </c>
       <c r="O8">
-        <v>19.607380608</v>
+        <v>19.301104256</v>
       </c>
       <c r="P8">
-        <v>41.665683792</v>
+        <v>41.014846544</v>
       </c>
       <c r="Q8">
-        <v>41.841683792</v>
+        <v>41.190846544</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09102173408070624</v>
+        <v>0.09135886044644324</v>
       </c>
       <c r="T8">
-        <v>0.5893907919568747</v>
+        <v>0.5937846786516365</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.32</v>
       </c>
       <c r="W8">
-        <v>0.034204</v>
+        <v>0.035224</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>13.89705219325642</v>
+        <v>11.56682391595363</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08742942021519221</v>
+        <v>0.08718497039452057</v>
       </c>
       <c r="C9">
-        <v>1519.930867728444</v>
+        <v>1513.817574183708</v>
       </c>
       <c r="D9">
-        <v>1630.124867728444</v>
+        <v>1639.753574183708</v>
       </c>
       <c r="E9">
-        <v>5.894000000000005</v>
+        <v>21.636</v>
       </c>
       <c r="F9">
-        <v>110.194</v>
+        <v>125.936</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2013,28 +2013,28 @@
         <v>66.024</v>
       </c>
       <c r="M9">
-        <v>5.7080492</v>
+        <v>6.5234848</v>
       </c>
       <c r="N9">
-        <v>60.3159508</v>
+        <v>59.5005152</v>
       </c>
       <c r="O9">
-        <v>19.301104256</v>
+        <v>19.040164864</v>
       </c>
       <c r="P9">
-        <v>41.014846544</v>
+        <v>40.460350336</v>
       </c>
       <c r="Q9">
-        <v>41.190846544</v>
+        <v>40.63635033600001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09135886044644324</v>
+        <v>0.091703315646218</v>
       </c>
       <c r="T9">
-        <v>0.5937846786516365</v>
+        <v>0.5982740846223713</v>
       </c>
       <c r="U9">
         <v>0.0518</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.56682391595363</v>
+        <v>10.12097092645943</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08718497039452057</v>
+        <v>0.08704456057384891</v>
       </c>
       <c r="C10">
-        <v>1513.817574183708</v>
+        <v>1503.657825566519</v>
       </c>
       <c r="D10">
-        <v>1639.753574183708</v>
+        <v>1645.33582556652</v>
       </c>
       <c r="E10">
-        <v>21.636</v>
+        <v>37.37799999999999</v>
       </c>
       <c r="F10">
-        <v>125.936</v>
+        <v>141.678</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2095,45 +2095,45 @@
         <v>66.024</v>
       </c>
       <c r="M10">
-        <v>6.5234848</v>
+        <v>7.579772999999999</v>
       </c>
       <c r="N10">
-        <v>59.5005152</v>
+        <v>58.444227</v>
       </c>
       <c r="O10">
-        <v>19.040164864</v>
+        <v>18.70215264</v>
       </c>
       <c r="P10">
-        <v>40.460350336</v>
+        <v>39.74207436</v>
       </c>
       <c r="Q10">
-        <v>40.63635033600001</v>
+        <v>39.91807436</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.091703315646218</v>
+        <v>0.09205534128994385</v>
       </c>
       <c r="T10">
-        <v>0.5982740846223713</v>
+        <v>0.6028621588561992</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.32</v>
       </c>
       <c r="W10">
-        <v>0.035224</v>
+        <v>0.03638</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.12097092645943</v>
+        <v>8.710551094340161</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08704456057384891</v>
+        <v>0.08681167075317725</v>
       </c>
       <c r="C11">
-        <v>1503.657825566519</v>
+        <v>1497.259067583334</v>
       </c>
       <c r="D11">
-        <v>1645.33582556652</v>
+        <v>1654.679067583334</v>
       </c>
       <c r="E11">
-        <v>37.37799999999999</v>
+        <v>53.11999999999998</v>
       </c>
       <c r="F11">
-        <v>141.678</v>
+        <v>157.42</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2177,28 +2177,28 @@
         <v>66.024</v>
       </c>
       <c r="M11">
-        <v>7.579772999999999</v>
+        <v>8.42197</v>
       </c>
       <c r="N11">
-        <v>58.444227</v>
+        <v>57.60203</v>
       </c>
       <c r="O11">
-        <v>18.70215264</v>
+        <v>18.4326496</v>
       </c>
       <c r="P11">
-        <v>39.74207436</v>
+        <v>39.16938039999999</v>
       </c>
       <c r="Q11">
-        <v>39.91807436</v>
+        <v>39.3453804</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09205534128994385</v>
+        <v>0.09241518972575249</v>
       </c>
       <c r="T11">
-        <v>0.6028621588561992</v>
+        <v>0.6075521902952233</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.710551094340161</v>
+        <v>7.839495984906145</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08681167075317725</v>
+        <v>0.08663862093250557</v>
       </c>
       <c r="C12">
-        <v>1497.259067583334</v>
+        <v>1488.528614726116</v>
       </c>
       <c r="D12">
-        <v>1654.679067583334</v>
+        <v>1661.690614726116</v>
       </c>
       <c r="E12">
-        <v>53.12</v>
+        <v>68.86199999999999</v>
       </c>
       <c r="F12">
-        <v>157.42</v>
+        <v>173.162</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2259,45 +2259,45 @@
         <v>66.024</v>
       </c>
       <c r="M12">
-        <v>8.42197</v>
+        <v>9.402696600000001</v>
       </c>
       <c r="N12">
-        <v>57.60203</v>
+        <v>56.6213034</v>
       </c>
       <c r="O12">
-        <v>18.4326496</v>
+        <v>18.118817088</v>
       </c>
       <c r="P12">
-        <v>39.16938039999999</v>
+        <v>38.502486312</v>
       </c>
       <c r="Q12">
-        <v>39.3453804</v>
+        <v>38.678486312</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09241518972575249</v>
+        <v>0.09278312464326469</v>
       </c>
       <c r="T12">
-        <v>0.6075521902952233</v>
+        <v>0.6123476156991692</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.32</v>
       </c>
       <c r="W12">
-        <v>0.03638</v>
+        <v>0.036924</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>7.839495984906145</v>
+        <v>7.021815422609722</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08663862093250557</v>
+        <v>0.08641117111183391</v>
       </c>
       <c r="C13">
-        <v>1488.528614726116</v>
+        <v>1482.093197668293</v>
       </c>
       <c r="D13">
-        <v>1661.690614726116</v>
+        <v>1670.997197668293</v>
       </c>
       <c r="E13">
-        <v>68.86199999999999</v>
+        <v>84.60399999999998</v>
       </c>
       <c r="F13">
-        <v>173.162</v>
+        <v>188.904</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2341,28 +2341,28 @@
         <v>66.024</v>
       </c>
       <c r="M13">
-        <v>9.402696600000001</v>
+        <v>10.2574872</v>
       </c>
       <c r="N13">
-        <v>56.6213034</v>
+        <v>55.7665128</v>
       </c>
       <c r="O13">
-        <v>18.118817088</v>
+        <v>17.845284096</v>
       </c>
       <c r="P13">
-        <v>38.502486312</v>
+        <v>37.921228704</v>
       </c>
       <c r="Q13">
-        <v>38.678486312</v>
+        <v>38.097228704</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09278312464326469</v>
+        <v>0.09315942171799309</v>
       </c>
       <c r="T13">
-        <v>0.6123476156991692</v>
+        <v>0.6172520280441139</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.021815422609722</v>
+        <v>6.436664137392246</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08641117111183391</v>
+        <v>0.08627212129116227</v>
       </c>
       <c r="C14">
-        <v>1482.093197668293</v>
+        <v>1472.092232565057</v>
       </c>
       <c r="D14">
-        <v>1670.997197668293</v>
+        <v>1676.738232565057</v>
       </c>
       <c r="E14">
-        <v>84.60399999999998</v>
+        <v>100.346</v>
       </c>
       <c r="F14">
-        <v>188.904</v>
+        <v>204.646</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2423,45 +2423,45 @@
         <v>66.024</v>
       </c>
       <c r="M14">
-        <v>10.2574872</v>
+        <v>11.3169238</v>
       </c>
       <c r="N14">
-        <v>55.7665128</v>
+        <v>54.7070762</v>
       </c>
       <c r="O14">
-        <v>17.845284096</v>
+        <v>17.506264384</v>
       </c>
       <c r="P14">
-        <v>37.921228704</v>
+        <v>37.200811816</v>
       </c>
       <c r="Q14">
-        <v>38.097228704</v>
+        <v>37.376811816</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09315942171799309</v>
+        <v>0.0935443693001865</v>
       </c>
       <c r="T14">
-        <v>0.6172520280441139</v>
+        <v>0.6222691855004368</v>
       </c>
       <c r="U14">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V14">
         <v>0.32</v>
       </c>
       <c r="W14">
-        <v>0.036924</v>
+        <v>0.037604</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>6.436664137392246</v>
+        <v>5.834094243879242</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08627212129116227</v>
+        <v>0.0860514714704906</v>
       </c>
       <c r="C15">
-        <v>1472.092232565057</v>
+        <v>1465.541747230553</v>
       </c>
       <c r="D15">
-        <v>1676.738232565057</v>
+        <v>1685.929747230553</v>
       </c>
       <c r="E15">
-        <v>100.346</v>
+        <v>116.088</v>
       </c>
       <c r="F15">
-        <v>204.646</v>
+        <v>220.388</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2505,28 +2505,28 @@
         <v>66.024</v>
       </c>
       <c r="M15">
-        <v>11.3169238</v>
+        <v>12.1874564</v>
       </c>
       <c r="N15">
-        <v>54.7070762</v>
+        <v>53.8365436</v>
       </c>
       <c r="O15">
-        <v>17.506264384</v>
+        <v>17.227693952</v>
       </c>
       <c r="P15">
-        <v>37.200811816</v>
+        <v>36.608849648</v>
       </c>
       <c r="Q15">
-        <v>37.376811816</v>
+        <v>36.78484964800001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0935443693001865</v>
+        <v>0.09393826915173326</v>
       </c>
       <c r="T15">
-        <v>0.6222691855004368</v>
+        <v>0.6274030210371391</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.834094243879242</v>
+        <v>5.417373226459295</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0860514714704906</v>
+        <v>0.08583082164981894</v>
       </c>
       <c r="C16">
-        <v>1465.541747230553</v>
+        <v>1459.092589122373</v>
       </c>
       <c r="D16">
-        <v>1685.929747230553</v>
+        <v>1695.222589122373</v>
       </c>
       <c r="E16">
-        <v>116.088</v>
+        <v>131.83</v>
       </c>
       <c r="F16">
-        <v>220.388</v>
+        <v>236.1300000000001</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2587,28 +2587,28 @@
         <v>66.024</v>
       </c>
       <c r="M16">
-        <v>12.1874564</v>
+        <v>13.057989</v>
       </c>
       <c r="N16">
-        <v>53.8365436</v>
+        <v>52.96601099999999</v>
       </c>
       <c r="O16">
-        <v>17.227693952</v>
+        <v>16.94912352</v>
       </c>
       <c r="P16">
-        <v>36.608849648</v>
+        <v>36.01688747999999</v>
       </c>
       <c r="Q16">
-        <v>36.78484964800001</v>
+        <v>36.19288748</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09393826915173326</v>
+        <v>0.09434143723508111</v>
       </c>
       <c r="T16">
-        <v>0.6274030210371391</v>
+        <v>0.6326576527041169</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.417373226459295</v>
+        <v>5.056215011362009</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08583082164981894</v>
+        <v>0.08561017182914728</v>
       </c>
       <c r="C17">
-        <v>1459.092589122373</v>
+        <v>1452.746443073813</v>
       </c>
       <c r="D17">
-        <v>1695.222589122373</v>
+        <v>1704.618443073814</v>
       </c>
       <c r="E17">
-        <v>131.83</v>
+        <v>147.572</v>
       </c>
       <c r="F17">
-        <v>236.13</v>
+        <v>251.872</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2669,28 +2669,28 @@
         <v>66.024</v>
       </c>
       <c r="M17">
-        <v>13.057989</v>
+        <v>13.9285216</v>
       </c>
       <c r="N17">
-        <v>52.966011</v>
+        <v>52.0954784</v>
       </c>
       <c r="O17">
-        <v>16.94912352</v>
+        <v>16.670553088</v>
       </c>
       <c r="P17">
-        <v>36.01688748</v>
+        <v>35.424925312</v>
       </c>
       <c r="Q17">
-        <v>36.19288748</v>
+        <v>35.600925312</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09434143723508111</v>
+        <v>0.09475420455850866</v>
       </c>
       <c r="T17">
-        <v>0.6326576527041169</v>
+        <v>0.6380373946488798</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.05621501136201</v>
+        <v>4.740201573151884</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08561017182914728</v>
+        <v>0.0856785220084756</v>
       </c>
       <c r="C18">
-        <v>1452.746443073813</v>
+        <v>1434.082795770894</v>
       </c>
       <c r="D18">
-        <v>1704.618443073814</v>
+        <v>1701.696795770894</v>
       </c>
       <c r="E18">
-        <v>147.572</v>
+        <v>163.314</v>
       </c>
       <c r="F18">
-        <v>251.872</v>
+        <v>267.614</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2751,45 +2751,45 @@
         <v>66.024</v>
       </c>
       <c r="M18">
-        <v>13.9285216</v>
+        <v>15.4680892</v>
       </c>
       <c r="N18">
-        <v>52.0954784</v>
+        <v>50.5559108</v>
       </c>
       <c r="O18">
-        <v>16.670553088</v>
+        <v>16.177891456</v>
       </c>
       <c r="P18">
-        <v>35.424925312</v>
+        <v>34.37801934399999</v>
       </c>
       <c r="Q18">
-        <v>35.600925312</v>
+        <v>34.554019344</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09475420455850866</v>
+        <v>0.09517691808250074</v>
       </c>
       <c r="T18">
-        <v>0.6380373946488798</v>
+        <v>0.643546768929661</v>
       </c>
       <c r="U18">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V18">
         <v>0.32</v>
       </c>
       <c r="W18">
-        <v>0.037604</v>
+        <v>0.039304</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.740201573151884</v>
+        <v>4.268400520990013</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0856785220084756</v>
+        <v>0.08547487218780395</v>
       </c>
       <c r="C19">
-        <v>1434.082795770894</v>
+        <v>1427.075549739498</v>
       </c>
       <c r="D19">
-        <v>1701.696795770894</v>
+        <v>1710.431549739498</v>
       </c>
       <c r="E19">
-        <v>163.314</v>
+        <v>179.056</v>
       </c>
       <c r="F19">
-        <v>267.614</v>
+        <v>283.3560000000001</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2833,28 +2833,28 @@
         <v>66.024</v>
       </c>
       <c r="M19">
-        <v>15.4680892</v>
+        <v>16.3779768</v>
       </c>
       <c r="N19">
-        <v>50.5559108</v>
+        <v>49.6460232</v>
       </c>
       <c r="O19">
-        <v>16.177891456</v>
+        <v>15.886727424</v>
       </c>
       <c r="P19">
-        <v>34.37801934399999</v>
+        <v>33.759295776</v>
       </c>
       <c r="Q19">
-        <v>34.554019344</v>
+        <v>33.935295776</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09517691808250074</v>
+        <v>0.09560994169244384</v>
       </c>
       <c r="T19">
-        <v>0.643546768929661</v>
+        <v>0.6491905181929003</v>
       </c>
       <c r="U19">
         <v>0.0578</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.268400520990013</v>
+        <v>4.03126715871279</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08547487218780395</v>
+        <v>0.0857234223671323</v>
       </c>
       <c r="C20">
-        <v>1427.075549739498</v>
+        <v>1400.684961937902</v>
       </c>
       <c r="D20">
-        <v>1710.431549739498</v>
+        <v>1699.782961937902</v>
       </c>
       <c r="E20">
-        <v>179.056</v>
+        <v>194.798</v>
       </c>
       <c r="F20">
-        <v>283.356</v>
+        <v>299.098</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2915,45 +2915,45 @@
         <v>66.024</v>
       </c>
       <c r="M20">
-        <v>16.3779768</v>
+        <v>18.3347074</v>
       </c>
       <c r="N20">
-        <v>49.6460232</v>
+        <v>47.6892926</v>
       </c>
       <c r="O20">
-        <v>15.886727424</v>
+        <v>15.260573632</v>
       </c>
       <c r="P20">
-        <v>33.759295776</v>
+        <v>32.428718968</v>
       </c>
       <c r="Q20">
-        <v>33.935295776</v>
+        <v>32.604718968</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09560994169244384</v>
+        <v>0.0960536572433732</v>
       </c>
       <c r="T20">
-        <v>0.6491905181929003</v>
+        <v>0.6549736192897999</v>
       </c>
       <c r="U20">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V20">
         <v>0.32</v>
       </c>
       <c r="W20">
-        <v>0.039304</v>
+        <v>0.041684</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.03126715871279</v>
+        <v>3.601039196295001</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0857234223671323</v>
+        <v>0.08592437254646064</v>
       </c>
       <c r="C21">
-        <v>1400.684961937902</v>
+        <v>1376.430138699976</v>
       </c>
       <c r="D21">
-        <v>1699.782961937902</v>
+        <v>1691.270138699977</v>
       </c>
       <c r="E21">
-        <v>194.798</v>
+        <v>210.54</v>
       </c>
       <c r="F21">
-        <v>299.098</v>
+        <v>314.84</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2997,45 +2997,45 @@
         <v>66.024</v>
       </c>
       <c r="M21">
-        <v>18.3347074</v>
+        <v>20.181244</v>
       </c>
       <c r="N21">
-        <v>47.6892926</v>
+        <v>45.84275599999999</v>
       </c>
       <c r="O21">
-        <v>15.260573632</v>
+        <v>14.66968192</v>
       </c>
       <c r="P21">
-        <v>32.428718968</v>
+        <v>31.17307408</v>
       </c>
       <c r="Q21">
-        <v>32.604718968</v>
+        <v>31.34907407999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0960536572433732</v>
+        <v>0.09650846568307579</v>
       </c>
       <c r="T21">
-        <v>0.6549736192897999</v>
+        <v>0.660901297914122</v>
       </c>
       <c r="U21">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V21">
         <v>0.32</v>
       </c>
       <c r="W21">
-        <v>0.041684</v>
+        <v>0.043588</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.601039196295001</v>
+        <v>3.271552536602798</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08592437254646064</v>
+        <v>0.08576356272578899</v>
       </c>
       <c r="C22">
-        <v>1376.430138699976</v>
+        <v>1367.493659258236</v>
       </c>
       <c r="D22">
-        <v>1691.270138699977</v>
+        <v>1698.075659258236</v>
       </c>
       <c r="E22">
-        <v>210.54</v>
+        <v>226.282</v>
       </c>
       <c r="F22">
-        <v>314.84</v>
+        <v>330.5820000000001</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3079,28 +3079,28 @@
         <v>66.024</v>
       </c>
       <c r="M22">
-        <v>20.181244</v>
+        <v>21.19030620000001</v>
       </c>
       <c r="N22">
-        <v>45.84275599999999</v>
+        <v>44.83369379999999</v>
       </c>
       <c r="O22">
-        <v>14.66968192</v>
+        <v>14.346782016</v>
       </c>
       <c r="P22">
-        <v>31.17307408</v>
+        <v>30.48691178399999</v>
       </c>
       <c r="Q22">
-        <v>31.34907407999999</v>
+        <v>30.66291178399999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09650846568307579</v>
+        <v>0.09697478826049237</v>
       </c>
       <c r="T22">
-        <v>0.660901297914122</v>
+        <v>0.6669790443517181</v>
       </c>
       <c r="U22">
         <v>0.0641</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.271552536602798</v>
+        <v>3.115764320574093</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08576356272578899</v>
+        <v>0.08676963290511731</v>
       </c>
       <c r="C23">
-        <v>1367.493659258236</v>
+        <v>1310.052889660288</v>
       </c>
       <c r="D23">
-        <v>1698.075659258236</v>
+        <v>1656.376889660288</v>
       </c>
       <c r="E23">
-        <v>226.282</v>
+        <v>242.024</v>
       </c>
       <c r="F23">
-        <v>330.582</v>
+        <v>346.324</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3161,45 +3161,45 @@
         <v>66.024</v>
       </c>
       <c r="M23">
-        <v>21.1903062</v>
+        <v>24.9006956</v>
       </c>
       <c r="N23">
-        <v>44.8336938</v>
+        <v>41.12330439999999</v>
       </c>
       <c r="O23">
-        <v>14.346782016</v>
+        <v>13.159457408</v>
       </c>
       <c r="P23">
-        <v>30.486911784</v>
+        <v>27.963846992</v>
       </c>
       <c r="Q23">
-        <v>30.662911784</v>
+        <v>28.139846992</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09697478826049237</v>
+        <v>0.09745306782707348</v>
       </c>
       <c r="T23">
-        <v>0.6669790443517181</v>
+        <v>0.6732126304415602</v>
       </c>
       <c r="U23">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V23">
         <v>0.32</v>
       </c>
       <c r="W23">
-        <v>0.043588</v>
+        <v>0.048892</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>3.115764320574093</v>
+        <v>2.651492193655827</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08676963290511731</v>
+        <v>0.08666186308444565</v>
       </c>
       <c r="C24">
-        <v>1310.052889660288</v>
+        <v>1298.679448186229</v>
       </c>
       <c r="D24">
-        <v>1656.376889660288</v>
+        <v>1660.745448186229</v>
       </c>
       <c r="E24">
-        <v>242.024</v>
+        <v>257.766</v>
       </c>
       <c r="F24">
-        <v>346.324</v>
+        <v>362.066</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3243,28 +3243,28 @@
         <v>66.024</v>
       </c>
       <c r="M24">
-        <v>24.9006956</v>
+        <v>26.0325454</v>
       </c>
       <c r="N24">
-        <v>41.12330439999999</v>
+        <v>39.9914546</v>
       </c>
       <c r="O24">
-        <v>13.159457408</v>
+        <v>12.797265472</v>
       </c>
       <c r="P24">
-        <v>27.963846992</v>
+        <v>27.194189128</v>
       </c>
       <c r="Q24">
-        <v>28.139846992</v>
+        <v>27.370189128</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09745306782707348</v>
+        <v>0.09794377023953979</v>
       </c>
       <c r="T24">
-        <v>0.6732126304415602</v>
+        <v>0.6796081278584111</v>
       </c>
       <c r="U24">
         <v>0.07190000000000001</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.651492193655827</v>
+        <v>2.536209924366443</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08666186308444565</v>
+        <v>0.087190573263774</v>
       </c>
       <c r="C25">
-        <v>1298.679448186229</v>
+        <v>1261.723607582147</v>
       </c>
       <c r="D25">
-        <v>1660.745448186229</v>
+        <v>1639.531607582147</v>
       </c>
       <c r="E25">
-        <v>257.766</v>
+        <v>273.508</v>
       </c>
       <c r="F25">
-        <v>362.066</v>
+        <v>377.808</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3325,45 +3325,45 @@
         <v>66.024</v>
       </c>
       <c r="M25">
-        <v>26.0325454</v>
+        <v>28.6378464</v>
       </c>
       <c r="N25">
-        <v>39.9914546</v>
+        <v>37.3861536</v>
       </c>
       <c r="O25">
-        <v>12.797265472</v>
+        <v>11.963569152</v>
       </c>
       <c r="P25">
-        <v>27.194189128</v>
+        <v>25.422584448</v>
       </c>
       <c r="Q25">
-        <v>27.370189128</v>
+        <v>25.598584448</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09794377023953979</v>
+        <v>0.09844738587338683</v>
       </c>
       <c r="T25">
-        <v>0.6796081278584111</v>
+        <v>0.6861719278388635</v>
       </c>
       <c r="U25">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V25">
         <v>0.32</v>
       </c>
       <c r="W25">
-        <v>0.048892</v>
+        <v>0.051544</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.536209924366443</v>
+        <v>2.305480624408964</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.087190573263774</v>
+        <v>0.08710932344310232</v>
       </c>
       <c r="C26">
-        <v>1261.723607582147</v>
+        <v>1249.206343259193</v>
       </c>
       <c r="D26">
-        <v>1639.531607582147</v>
+        <v>1642.756343259193</v>
       </c>
       <c r="E26">
-        <v>273.508</v>
+        <v>289.25</v>
       </c>
       <c r="F26">
-        <v>377.808</v>
+        <v>393.55</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3407,28 +3407,28 @@
         <v>66.024</v>
       </c>
       <c r="M26">
-        <v>28.6378464</v>
+        <v>29.83109</v>
       </c>
       <c r="N26">
-        <v>37.3861536</v>
+        <v>36.19291</v>
       </c>
       <c r="O26">
-        <v>11.963569152</v>
+        <v>11.5817312</v>
       </c>
       <c r="P26">
-        <v>25.422584448</v>
+        <v>24.6111788</v>
       </c>
       <c r="Q26">
-        <v>25.598584448</v>
+        <v>24.7871788</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09844738587338683</v>
+        <v>0.09896443125746977</v>
       </c>
       <c r="T26">
-        <v>0.6861719278388635</v>
+        <v>0.6929107624854612</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.305480624408964</v>
+        <v>2.213261399432605</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08710932344310232</v>
+        <v>0.08702807362243067</v>
       </c>
       <c r="C27">
-        <v>1249.206343259193</v>
+        <v>1236.701789168487</v>
       </c>
       <c r="D27">
-        <v>1642.756343259193</v>
+        <v>1645.993789168487</v>
       </c>
       <c r="E27">
-        <v>289.25</v>
+        <v>304.992</v>
       </c>
       <c r="F27">
-        <v>393.55</v>
+        <v>409.292</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3489,28 +3489,28 @@
         <v>66.024</v>
       </c>
       <c r="M27">
-        <v>29.83109</v>
+        <v>31.02433360000001</v>
       </c>
       <c r="N27">
-        <v>36.19291</v>
+        <v>34.9996664</v>
       </c>
       <c r="O27">
-        <v>11.5817312</v>
+        <v>11.199893248</v>
       </c>
       <c r="P27">
-        <v>24.6111788</v>
+        <v>23.799773152</v>
       </c>
       <c r="Q27">
-        <v>24.7871788</v>
+        <v>23.975773152</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09896443125746977</v>
+        <v>0.09949545084112253</v>
       </c>
       <c r="T27">
-        <v>0.6929107624854612</v>
+        <v>0.6998317277981833</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.213261399432605</v>
+        <v>2.128135960992889</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08702807362243067</v>
+        <v>0.08694682380175903</v>
       </c>
       <c r="C28">
-        <v>1236.701789168487</v>
+        <v>1224.210020604112</v>
       </c>
       <c r="D28">
-        <v>1645.993789168487</v>
+        <v>1649.244020604112</v>
       </c>
       <c r="E28">
-        <v>304.992</v>
+        <v>320.734</v>
       </c>
       <c r="F28">
-        <v>409.292</v>
+        <v>425.034</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3571,28 +3571,28 @@
         <v>66.024</v>
       </c>
       <c r="M28">
-        <v>31.02433360000001</v>
+        <v>32.21757720000001</v>
       </c>
       <c r="N28">
-        <v>34.9996664</v>
+        <v>33.80642279999999</v>
       </c>
       <c r="O28">
-        <v>11.199893248</v>
+        <v>10.818055296</v>
       </c>
       <c r="P28">
-        <v>23.799773152</v>
+        <v>22.988367504</v>
       </c>
       <c r="Q28">
-        <v>23.975773152</v>
+        <v>23.16436750399999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09949545084112253</v>
+        <v>0.1000410189065192</v>
       </c>
       <c r="T28">
-        <v>0.6998317277981833</v>
+        <v>0.706942308598925</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.128135960992889</v>
+        <v>2.049316110585745</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08694682380175903</v>
+        <v>0.08956925398108735</v>
       </c>
       <c r="C29">
-        <v>1224.210020604112</v>
+        <v>1109.653741188295</v>
       </c>
       <c r="D29">
-        <v>1649.244020604112</v>
+        <v>1550.429741188295</v>
       </c>
       <c r="E29">
-        <v>320.734</v>
+        <v>336.4760000000001</v>
       </c>
       <c r="F29">
-        <v>425.034</v>
+        <v>440.7760000000001</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3653,45 +3653,45 @@
         <v>66.024</v>
       </c>
       <c r="M29">
-        <v>32.21757720000001</v>
+        <v>39.66984000000001</v>
       </c>
       <c r="N29">
-        <v>33.80642279999999</v>
+        <v>26.35415999999999</v>
       </c>
       <c r="O29">
-        <v>10.818055296</v>
+        <v>8.433331199999998</v>
       </c>
       <c r="P29">
-        <v>22.988367504</v>
+        <v>17.9208288</v>
       </c>
       <c r="Q29">
-        <v>23.16436750399999</v>
+        <v>18.09682879999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1000410189065192</v>
+        <v>0.1006017416403991</v>
       </c>
       <c r="T29">
-        <v>0.706942308598925</v>
+        <v>0.7142504055330208</v>
       </c>
       <c r="U29">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V29">
         <v>0.32</v>
       </c>
       <c r="W29">
-        <v>0.051544</v>
+        <v>0.06119999999999999</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.049316110585745</v>
+        <v>1.664337441239994</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08956925398108735</v>
+        <v>0.08958456416041569</v>
       </c>
       <c r="C30">
-        <v>1109.653741188295</v>
+        <v>1093.369601330819</v>
       </c>
       <c r="D30">
-        <v>1550.429741188295</v>
+        <v>1549.887601330819</v>
       </c>
       <c r="E30">
-        <v>336.4760000000001</v>
+        <v>352.2180000000001</v>
       </c>
       <c r="F30">
-        <v>440.7760000000001</v>
+        <v>456.5180000000001</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3735,28 +3735,28 @@
         <v>66.024</v>
       </c>
       <c r="M30">
-        <v>39.66984000000001</v>
+        <v>41.08662</v>
       </c>
       <c r="N30">
-        <v>26.35415999999999</v>
+        <v>24.93738</v>
       </c>
       <c r="O30">
-        <v>8.433331199999998</v>
+        <v>7.979961599999999</v>
       </c>
       <c r="P30">
-        <v>17.9208288</v>
+        <v>16.9574184</v>
       </c>
       <c r="Q30">
-        <v>18.09682879999999</v>
+        <v>17.1334184</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1006017416403991</v>
+        <v>0.1011782593808672</v>
       </c>
       <c r="T30">
-        <v>0.7142504055330208</v>
+        <v>0.7217643643525838</v>
       </c>
       <c r="U30">
         <v>0.09</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.664337441239994</v>
+        <v>1.60694649499034</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08958456416041569</v>
+        <v>0.08959987433974402</v>
       </c>
       <c r="C31">
-        <v>1093.369601330819</v>
+        <v>1077.085840481665</v>
       </c>
       <c r="D31">
-        <v>1549.887601330819</v>
+        <v>1549.345840481665</v>
       </c>
       <c r="E31">
-        <v>352.218</v>
+        <v>367.96</v>
       </c>
       <c r="F31">
-        <v>456.518</v>
+        <v>472.26</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3817,28 +3817,28 @@
         <v>66.024</v>
       </c>
       <c r="M31">
-        <v>41.08662</v>
+        <v>42.5034</v>
       </c>
       <c r="N31">
-        <v>24.93738</v>
+        <v>23.5206</v>
       </c>
       <c r="O31">
-        <v>7.979961600000002</v>
+        <v>7.526592000000001</v>
       </c>
       <c r="P31">
-        <v>16.9574184</v>
+        <v>15.994008</v>
       </c>
       <c r="Q31">
-        <v>17.1334184</v>
+        <v>16.170008</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1011782593808672</v>
+        <v>0.1017712490567772</v>
       </c>
       <c r="T31">
-        <v>0.7217643643525838</v>
+        <v>0.7294930077098489</v>
       </c>
       <c r="U31">
         <v>0.09</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.60694649499034</v>
+        <v>1.553381611823995</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08959987433974402</v>
+        <v>0.08961518451907236</v>
       </c>
       <c r="C32">
-        <v>1077.085840481665</v>
+        <v>1060.802458243527</v>
       </c>
       <c r="D32">
-        <v>1549.345840481665</v>
+        <v>1548.804458243527</v>
       </c>
       <c r="E32">
-        <v>367.96</v>
+        <v>383.702</v>
       </c>
       <c r="F32">
-        <v>472.26</v>
+        <v>488.002</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3899,28 +3899,28 @@
         <v>66.024</v>
       </c>
       <c r="M32">
-        <v>42.5034</v>
+        <v>43.92018</v>
       </c>
       <c r="N32">
-        <v>23.5206</v>
+        <v>22.10382</v>
       </c>
       <c r="O32">
-        <v>7.526592000000001</v>
+        <v>7.0732224</v>
       </c>
       <c r="P32">
-        <v>15.994008</v>
+        <v>15.0305976</v>
       </c>
       <c r="Q32">
-        <v>16.170008</v>
+        <v>15.2065976</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1017712490567772</v>
+        <v>0.1023814268392353</v>
       </c>
       <c r="T32">
-        <v>0.7294930077098489</v>
+        <v>0.7374456697151506</v>
       </c>
       <c r="U32">
         <v>0.09</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.553381611823995</v>
+        <v>1.503272527571608</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08961518451907236</v>
+        <v>0.1040769323079715</v>
       </c>
       <c r="C33">
-        <v>1060.802458243527</v>
+        <v>660.7159403977131</v>
       </c>
       <c r="D33">
-        <v>1548.804458243527</v>
+        <v>1164.459940397713</v>
       </c>
       <c r="E33">
-        <v>383.702</v>
+        <v>399.444</v>
       </c>
       <c r="F33">
-        <v>488.002</v>
+        <v>503.744</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -3981,45 +3981,45 @@
         <v>66.024</v>
       </c>
       <c r="M33">
-        <v>43.92018</v>
+        <v>73.94961920000001</v>
       </c>
       <c r="N33">
-        <v>22.10382</v>
+        <v>-7.925619200000014</v>
       </c>
       <c r="O33">
-        <v>7.0732224</v>
+        <v>-2.536198144000005</v>
       </c>
       <c r="P33">
-        <v>15.0305976</v>
+        <v>-5.38942105600001</v>
       </c>
       <c r="Q33">
-        <v>15.2065976</v>
+        <v>-5.213421056000009</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1023814268392353</v>
+        <v>0.1037090432854865</v>
       </c>
       <c r="T33">
-        <v>0.7374456697151506</v>
+        <v>0.7547489625803566</v>
       </c>
       <c r="U33">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.32</v>
+        <v>0.2857037024471926</v>
       </c>
       <c r="W33">
-        <v>0.06119999999999999</v>
+        <v>0.1048586964807521</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y33">
-        <v>1.503272527571608</v>
+        <v>0.8928240701474767</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1040769323079715</v>
+        <v>0.1050869323079715</v>
       </c>
       <c r="C34">
-        <v>660.7159403977131</v>
+        <v>625.1364400579704</v>
       </c>
       <c r="D34">
-        <v>1164.459940397713</v>
+        <v>1144.62244005797</v>
       </c>
       <c r="E34">
-        <v>399.444</v>
+        <v>415.186</v>
       </c>
       <c r="F34">
-        <v>503.744</v>
+        <v>519.486</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4063,37 +4063,37 @@
         <v>66.024</v>
       </c>
       <c r="M34">
-        <v>73.94961920000001</v>
+        <v>76.26054480000001</v>
       </c>
       <c r="N34">
-        <v>-7.925619200000014</v>
+        <v>-10.2365448</v>
       </c>
       <c r="O34">
-        <v>-2.536198144000005</v>
+        <v>-3.275694336000001</v>
       </c>
       <c r="P34">
-        <v>-5.38942105600001</v>
+        <v>-6.960850464000004</v>
       </c>
       <c r="Q34">
-        <v>-5.213421056000009</v>
+        <v>-6.784850464000003</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1037090432854865</v>
+        <v>0.1045733573643743</v>
       </c>
       <c r="T34">
-        <v>0.7547489625803566</v>
+        <v>0.7660138724696157</v>
       </c>
       <c r="U34">
         <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.2857037024471926</v>
+        <v>0.2770460144942474</v>
       </c>
       <c r="W34">
-        <v>0.1048586964807521</v>
+        <v>0.1061296450722445</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8928240701474767</v>
+        <v>0.865768795294523</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1050869323079715</v>
+        <v>0.1060969323079715</v>
       </c>
       <c r="C35">
-        <v>625.1364400579704</v>
+        <v>590.22151334001</v>
       </c>
       <c r="D35">
-        <v>1144.62244005797</v>
+        <v>1125.44951334001</v>
       </c>
       <c r="E35">
-        <v>415.186</v>
+        <v>430.9280000000001</v>
       </c>
       <c r="F35">
-        <v>519.486</v>
+        <v>535.2280000000001</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4145,37 +4145,37 @@
         <v>66.024</v>
       </c>
       <c r="M35">
-        <v>76.26054480000001</v>
+        <v>78.57147040000002</v>
       </c>
       <c r="N35">
-        <v>-10.2365448</v>
+        <v>-12.54747040000002</v>
       </c>
       <c r="O35">
-        <v>-3.275694336000001</v>
+        <v>-4.015190528000008</v>
       </c>
       <c r="P35">
-        <v>-6.960850464000004</v>
+        <v>-8.532279872000014</v>
       </c>
       <c r="Q35">
-        <v>-6.784850464000003</v>
+        <v>-8.356279872000014</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1045733573643743</v>
+        <v>0.105463862778986</v>
       </c>
       <c r="T35">
-        <v>0.7660138724696157</v>
+        <v>0.7776201432646099</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.2770460144942474</v>
+        <v>0.26889760230324</v>
       </c>
       <c r="W35">
-        <v>0.1061296450722445</v>
+        <v>0.1073258319818844</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.865768795294523</v>
+        <v>0.840305007197625</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1060969323079715</v>
+        <v>0.1071069323079715</v>
       </c>
       <c r="C36">
-        <v>590.22151334001</v>
+        <v>555.9383147237875</v>
       </c>
       <c r="D36">
-        <v>1125.44951334001</v>
+        <v>1106.908314723787</v>
       </c>
       <c r="E36">
-        <v>430.9280000000001</v>
+        <v>446.67</v>
       </c>
       <c r="F36">
-        <v>535.2280000000001</v>
+        <v>550.97</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4227,37 +4227,37 @@
         <v>66.024</v>
       </c>
       <c r="M36">
-        <v>78.57147040000002</v>
+        <v>80.88239600000001</v>
       </c>
       <c r="N36">
-        <v>-12.54747040000002</v>
+        <v>-14.85839600000001</v>
       </c>
       <c r="O36">
-        <v>-4.015190528000008</v>
+        <v>-4.754686720000004</v>
       </c>
       <c r="P36">
-        <v>-8.532279872000014</v>
+        <v>-10.10370928000001</v>
       </c>
       <c r="Q36">
-        <v>-8.356279872000014</v>
+        <v>-9.927709280000009</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.105463862778986</v>
+        <v>0.1063817683602012</v>
       </c>
       <c r="T36">
-        <v>0.7776201432646099</v>
+        <v>0.7895835300840655</v>
       </c>
       <c r="U36">
         <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.26889760230324</v>
+        <v>0.2612148136660046</v>
       </c>
       <c r="W36">
-        <v>0.1073258319818844</v>
+        <v>0.1084536653538305</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.840305007197625</v>
+        <v>0.8162962927062645</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1071069323079715</v>
+        <v>0.1286225232162942</v>
       </c>
       <c r="C37">
-        <v>555.9383147237875</v>
+        <v>252.644263086552</v>
       </c>
       <c r="D37">
-        <v>1106.908314723787</v>
+        <v>819.3562630865521</v>
       </c>
       <c r="E37">
-        <v>446.67</v>
+        <v>462.4120000000001</v>
       </c>
       <c r="F37">
-        <v>550.97</v>
+        <v>566.7120000000001</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4309,45 +4309,45 @@
         <v>66.024</v>
       </c>
       <c r="M37">
-        <v>80.88239600000001</v>
+        <v>113.7957696</v>
       </c>
       <c r="N37">
-        <v>-14.85839600000001</v>
+        <v>-47.77176960000003</v>
       </c>
       <c r="O37">
-        <v>-4.754686720000004</v>
+        <v>-15.28696627200001</v>
       </c>
       <c r="P37">
-        <v>-10.10370928000001</v>
+        <v>-32.48480332800002</v>
       </c>
       <c r="Q37">
-        <v>-9.927709280000009</v>
+        <v>-32.30880332800002</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1063817683602012</v>
+        <v>0.1089933442850836</v>
       </c>
       <c r="T37">
-        <v>0.7895835300840655</v>
+        <v>0.8236211191750743</v>
       </c>
       <c r="U37">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.2612148136660046</v>
+        <v>0.1856631408554576</v>
       </c>
       <c r="W37">
-        <v>0.1084536653538305</v>
+        <v>0.1635188413162241</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y37">
-        <v>0.8162962927062645</v>
+        <v>0.5801973151733049</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1286225232162942</v>
+        <v>0.1301725232162942</v>
       </c>
       <c r="C38">
-        <v>252.6442630865521</v>
+        <v>221.849943215444</v>
       </c>
       <c r="D38">
-        <v>819.3562630865521</v>
+        <v>804.3039432154441</v>
       </c>
       <c r="E38">
-        <v>462.412</v>
+        <v>478.1540000000001</v>
       </c>
       <c r="F38">
-        <v>566.712</v>
+        <v>582.4540000000001</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4391,37 +4391,37 @@
         <v>66.024</v>
       </c>
       <c r="M38">
-        <v>113.7957696</v>
+        <v>116.9567632</v>
       </c>
       <c r="N38">
-        <v>-47.7717696</v>
+        <v>-50.93276320000001</v>
       </c>
       <c r="O38">
-        <v>-15.286966272</v>
+        <v>-16.298484224</v>
       </c>
       <c r="P38">
-        <v>-32.484803328</v>
+        <v>-34.634278976</v>
       </c>
       <c r="Q38">
-        <v>-32.308803328</v>
+        <v>-34.458278976</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1089933442850836</v>
+        <v>0.1099964132419897</v>
       </c>
       <c r="T38">
-        <v>0.8236211191750742</v>
+        <v>0.8366944702730913</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.1856631408554576</v>
+        <v>0.1806452181296344</v>
       </c>
       <c r="W38">
-        <v>0.1635188413162241</v>
+        <v>0.1645264401995694</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.5801973151733051</v>
+        <v>0.5645163066551075</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1301725232162942</v>
+        <v>0.1317225232162942</v>
       </c>
       <c r="C39">
-        <v>221.849943215444</v>
+        <v>191.5986962180567</v>
       </c>
       <c r="D39">
-        <v>804.3039432154441</v>
+        <v>789.7946962180567</v>
       </c>
       <c r="E39">
-        <v>478.1540000000001</v>
+        <v>493.896</v>
       </c>
       <c r="F39">
-        <v>582.4540000000001</v>
+        <v>598.196</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4473,37 +4473,37 @@
         <v>66.024</v>
       </c>
       <c r="M39">
-        <v>116.9567632</v>
+        <v>120.1177568</v>
       </c>
       <c r="N39">
-        <v>-50.93276320000001</v>
+        <v>-54.09375680000001</v>
       </c>
       <c r="O39">
-        <v>-16.298484224</v>
+        <v>-17.310002176</v>
       </c>
       <c r="P39">
-        <v>-34.634278976</v>
+        <v>-36.783754624</v>
       </c>
       <c r="Q39">
-        <v>-34.458278976</v>
+        <v>-36.607754624</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1099964132419897</v>
+        <v>0.1110318392620218</v>
       </c>
       <c r="T39">
-        <v>0.8366944702730913</v>
+        <v>0.8501895423742702</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1806452181296344</v>
+        <v>0.1758913965999072</v>
       </c>
       <c r="W39">
-        <v>0.1645264401995694</v>
+        <v>0.1654810075627386</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5645163066551075</v>
+        <v>0.54966061437471</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1317225232162942</v>
+        <v>0.1332725232162942</v>
       </c>
       <c r="C40">
-        <v>191.5986962180567</v>
+        <v>161.8616525846298</v>
       </c>
       <c r="D40">
-        <v>789.7946962180567</v>
+        <v>775.7996525846298</v>
       </c>
       <c r="E40">
-        <v>493.896</v>
+        <v>509.638</v>
       </c>
       <c r="F40">
-        <v>598.196</v>
+        <v>613.938</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4555,37 +4555,37 @@
         <v>66.024</v>
       </c>
       <c r="M40">
-        <v>120.1177568</v>
+        <v>123.2787504</v>
       </c>
       <c r="N40">
-        <v>-54.09375680000001</v>
+        <v>-57.25475040000001</v>
       </c>
       <c r="O40">
-        <v>-17.310002176</v>
+        <v>-18.321520128</v>
       </c>
       <c r="P40">
-        <v>-36.783754624</v>
+        <v>-38.933230272</v>
       </c>
       <c r="Q40">
-        <v>-36.607754624</v>
+        <v>-38.757230272</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1110318392620218</v>
+        <v>0.1121012136761533</v>
       </c>
       <c r="T40">
-        <v>0.8501895423742702</v>
+        <v>0.8641270758558157</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1758913965999072</v>
+        <v>0.1713813607896532</v>
       </c>
       <c r="W40">
-        <v>0.1654810075627386</v>
+        <v>0.1663866227534377</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.54966061437471</v>
+        <v>0.5355667524676662</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1332725232162942</v>
+        <v>0.1348225232162942</v>
       </c>
       <c r="C41">
-        <v>161.8616525846298</v>
+        <v>132.6119534309611</v>
       </c>
       <c r="D41">
-        <v>775.7996525846298</v>
+        <v>762.2919534309611</v>
       </c>
       <c r="E41">
-        <v>509.638</v>
+        <v>525.3800000000001</v>
       </c>
       <c r="F41">
-        <v>613.938</v>
+        <v>629.6800000000001</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4637,37 +4637,37 @@
         <v>66.024</v>
       </c>
       <c r="M41">
-        <v>123.2787504</v>
+        <v>126.439744</v>
       </c>
       <c r="N41">
-        <v>-57.25475040000001</v>
+        <v>-60.41574400000002</v>
       </c>
       <c r="O41">
-        <v>-18.321520128</v>
+        <v>-19.33303808000001</v>
       </c>
       <c r="P41">
-        <v>-38.933230272</v>
+        <v>-41.08270592000001</v>
       </c>
       <c r="Q41">
-        <v>-38.757230272</v>
+        <v>-40.90670592000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1121012136761533</v>
+        <v>0.1132062339040892</v>
       </c>
       <c r="T41">
-        <v>0.8641270758558157</v>
+        <v>0.8785291937867459</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1713813607896532</v>
+        <v>0.1670968267699118</v>
       </c>
       <c r="W41">
-        <v>0.1663866227534377</v>
+        <v>0.1672469571846017</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5355667524676662</v>
+        <v>0.5221775836559744</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1348225232162942</v>
+        <v>0.1363725232162942</v>
       </c>
       <c r="C42">
-        <v>132.6119534309611</v>
+        <v>103.824578455635</v>
       </c>
       <c r="D42">
-        <v>762.2919534309611</v>
+        <v>749.246578455635</v>
       </c>
       <c r="E42">
-        <v>525.3800000000001</v>
+        <v>541.1220000000001</v>
       </c>
       <c r="F42">
-        <v>629.6800000000001</v>
+        <v>645.422</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4719,37 +4719,37 @@
         <v>66.024</v>
       </c>
       <c r="M42">
-        <v>126.439744</v>
+        <v>129.6007376</v>
       </c>
       <c r="N42">
-        <v>-60.41574400000002</v>
+        <v>-63.5767376</v>
       </c>
       <c r="O42">
-        <v>-19.33303808000001</v>
+        <v>-20.344556032</v>
       </c>
       <c r="P42">
-        <v>-41.08270592000001</v>
+        <v>-43.232181568</v>
       </c>
       <c r="Q42">
-        <v>-40.90670592000001</v>
+        <v>-43.056181568</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1132062339040892</v>
+        <v>0.1143487124448365</v>
       </c>
       <c r="T42">
-        <v>0.8785291937867459</v>
+        <v>0.8934195191051655</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1670968267699118</v>
+        <v>0.1630212944096701</v>
       </c>
       <c r="W42">
-        <v>0.1672469571846017</v>
+        <v>0.1680653240825383</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5221775836559744</v>
+        <v>0.509441545030219</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1363725232162942</v>
+        <v>0.1530525020187133</v>
       </c>
       <c r="C43">
-        <v>103.824578455635</v>
+        <v>-28.44073625682245</v>
       </c>
       <c r="D43">
-        <v>749.246578455635</v>
+        <v>632.7232637431777</v>
       </c>
       <c r="E43">
-        <v>541.1220000000001</v>
+        <v>556.864</v>
       </c>
       <c r="F43">
-        <v>645.422</v>
+        <v>661.1640000000001</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4801,45 +4801,45 @@
         <v>66.024</v>
       </c>
       <c r="M43">
-        <v>129.6007376</v>
+        <v>155.9024712</v>
       </c>
       <c r="N43">
-        <v>-63.5767376</v>
+        <v>-89.87847120000004</v>
       </c>
       <c r="O43">
-        <v>-20.344556032</v>
+        <v>-28.76111078400001</v>
       </c>
       <c r="P43">
-        <v>-43.232181568</v>
+        <v>-61.11736041600003</v>
       </c>
       <c r="Q43">
-        <v>-43.056181568</v>
+        <v>-60.94136041600002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1143487124448365</v>
+        <v>0.1162719295601251</v>
       </c>
       <c r="T43">
-        <v>0.8934195191051655</v>
+        <v>0.9184854853209236</v>
       </c>
       <c r="U43">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.1630212944096701</v>
+        <v>0.1355185702790835</v>
       </c>
       <c r="W43">
-        <v>0.1680653240825383</v>
+        <v>0.2038447211281921</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y43">
-        <v>0.509441545030219</v>
+        <v>0.423495532122136</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1530525020187132</v>
+        <v>0.1549525020187132</v>
       </c>
       <c r="C44">
-        <v>-28.44073625682211</v>
+        <v>-55.19644807174632</v>
       </c>
       <c r="D44">
-        <v>632.7232637431779</v>
+        <v>621.7095519282537</v>
       </c>
       <c r="E44">
-        <v>556.864</v>
+        <v>572.606</v>
       </c>
       <c r="F44">
-        <v>661.164</v>
+        <v>676.9060000000001</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4883,37 +4883,37 @@
         <v>66.024</v>
       </c>
       <c r="M44">
-        <v>155.9024712</v>
+        <v>159.6144348</v>
       </c>
       <c r="N44">
-        <v>-89.87847120000001</v>
+        <v>-93.59043480000003</v>
       </c>
       <c r="O44">
-        <v>-28.761110784</v>
+        <v>-29.94893913600001</v>
       </c>
       <c r="P44">
-        <v>-61.117360416</v>
+        <v>-63.64149566400002</v>
       </c>
       <c r="Q44">
-        <v>-60.941360416</v>
+        <v>-63.46549566400002</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1162719295601251</v>
+        <v>0.1175082792015308</v>
       </c>
       <c r="T44">
-        <v>0.9184854853209236</v>
+        <v>0.9345992657651503</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.1355185702790835</v>
+        <v>0.1323669756214304</v>
       </c>
       <c r="W44">
-        <v>0.2038447211281921</v>
+        <v>0.2045878671484667</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4234955321221361</v>
+        <v>0.4136467988169701</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1549525020187132</v>
+        <v>0.1568525020187133</v>
       </c>
       <c r="C45">
-        <v>-55.19644807174632</v>
+        <v>-81.57529215171724</v>
       </c>
       <c r="D45">
-        <v>621.7095519282537</v>
+        <v>611.0727078482828</v>
       </c>
       <c r="E45">
-        <v>572.606</v>
+        <v>588.348</v>
       </c>
       <c r="F45">
-        <v>676.9060000000001</v>
+        <v>692.648</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4965,37 +4965,37 @@
         <v>66.024</v>
       </c>
       <c r="M45">
-        <v>159.6144348</v>
+        <v>163.3263984</v>
       </c>
       <c r="N45">
-        <v>-93.59043480000003</v>
+        <v>-97.30239840000002</v>
       </c>
       <c r="O45">
-        <v>-29.94893913600001</v>
+        <v>-31.13676748800001</v>
       </c>
       <c r="P45">
-        <v>-63.64149566400002</v>
+        <v>-66.16563091200001</v>
       </c>
       <c r="Q45">
-        <v>-63.46549566400002</v>
+        <v>-65.98963091200001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1175082792015308</v>
+        <v>0.1187887841872725</v>
       </c>
       <c r="T45">
-        <v>0.9345992657651503</v>
+        <v>0.9512885383680996</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.1323669756214304</v>
+        <v>0.1293586352663979</v>
       </c>
       <c r="W45">
-        <v>0.2045878671484667</v>
+        <v>0.2052972338041834</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.4136467988169701</v>
+        <v>0.4042457352074935</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1568525020187133</v>
+        <v>0.1587525020187133</v>
       </c>
       <c r="C46">
-        <v>-81.57529215171724</v>
+        <v>-107.5962866331266</v>
       </c>
       <c r="D46">
-        <v>611.0727078482828</v>
+        <v>600.7937133668734</v>
       </c>
       <c r="E46">
-        <v>588.348</v>
+        <v>604.0899999999999</v>
       </c>
       <c r="F46">
-        <v>692.648</v>
+        <v>708.39</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5047,37 +5047,37 @@
         <v>66.024</v>
       </c>
       <c r="M46">
-        <v>163.3263984</v>
+        <v>167.038362</v>
       </c>
       <c r="N46">
-        <v>-97.30239840000002</v>
+        <v>-101.014362</v>
       </c>
       <c r="O46">
-        <v>-31.13676748800001</v>
+        <v>-32.32459584</v>
       </c>
       <c r="P46">
-        <v>-66.16563091200001</v>
+        <v>-68.68976616</v>
       </c>
       <c r="Q46">
-        <v>-65.98963091200001</v>
+        <v>-68.51376616</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1187887841872725</v>
+        <v>0.1201158529906774</v>
       </c>
       <c r="T46">
-        <v>0.9512885383680996</v>
+        <v>0.9685846936111557</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.1293586352663979</v>
+        <v>0.1264839989271447</v>
       </c>
       <c r="W46">
-        <v>0.2052972338041834</v>
+        <v>0.2059750730529793</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4042457352074935</v>
+        <v>0.395262496647327</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1587525020187133</v>
+        <v>0.1606525020187132</v>
       </c>
       <c r="C47">
-        <v>-107.5962866331266</v>
+        <v>-133.2771911875179</v>
       </c>
       <c r="D47">
-        <v>600.7937133668734</v>
+        <v>590.8548088124821</v>
       </c>
       <c r="E47">
-        <v>604.0899999999999</v>
+        <v>619.8320000000001</v>
       </c>
       <c r="F47">
-        <v>708.39</v>
+        <v>724.1320000000001</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5129,37 +5129,37 @@
         <v>66.024</v>
       </c>
       <c r="M47">
-        <v>167.038362</v>
+        <v>170.7503256</v>
       </c>
       <c r="N47">
-        <v>-101.014362</v>
+        <v>-104.7263256</v>
       </c>
       <c r="O47">
-        <v>-32.32459584</v>
+        <v>-33.51242419200001</v>
       </c>
       <c r="P47">
-        <v>-68.68976616</v>
+        <v>-71.21390140800001</v>
       </c>
       <c r="Q47">
-        <v>-68.51376616</v>
+        <v>-71.03790140800001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1201158529906774</v>
+        <v>0.1214920724905048</v>
       </c>
       <c r="T47">
-        <v>0.9685846936111557</v>
+        <v>0.9865214471965476</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.1264839989271447</v>
+        <v>0.1237343467765545</v>
       </c>
       <c r="W47">
-        <v>0.2059750730529793</v>
+        <v>0.2066234410300884</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.395262496647327</v>
+        <v>0.3866698336767329</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1606525020187132</v>
+        <v>0.1625525020187133</v>
       </c>
       <c r="C48">
-        <v>-133.2771911875179</v>
+        <v>-158.6346094212429</v>
       </c>
       <c r="D48">
-        <v>590.8548088124821</v>
+        <v>581.2393905787571</v>
       </c>
       <c r="E48">
-        <v>619.8320000000001</v>
+        <v>635.5740000000001</v>
       </c>
       <c r="F48">
-        <v>724.1320000000001</v>
+        <v>739.874</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5211,37 +5211,37 @@
         <v>66.024</v>
       </c>
       <c r="M48">
-        <v>170.7503256</v>
+        <v>174.4622892</v>
       </c>
       <c r="N48">
-        <v>-104.7263256</v>
+        <v>-108.4382892</v>
       </c>
       <c r="O48">
-        <v>-33.51242419200001</v>
+        <v>-34.70025254400001</v>
       </c>
       <c r="P48">
-        <v>-71.21390140800001</v>
+        <v>-73.73803665600001</v>
       </c>
       <c r="Q48">
-        <v>-71.03790140800001</v>
+        <v>-73.562036656</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1214920724905048</v>
+        <v>0.1229202248016464</v>
       </c>
       <c r="T48">
-        <v>0.9865214471965476</v>
+        <v>1.005135059407803</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.1237343467765545</v>
+        <v>0.1211017011004576</v>
       </c>
       <c r="W48">
-        <v>0.2066234410300884</v>
+        <v>0.2072442188805121</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3866698336767329</v>
+        <v>0.3784428159389301</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1625525020187133</v>
+        <v>0.1644525020187133</v>
       </c>
       <c r="C49">
-        <v>-158.6346094212429</v>
+        <v>-183.6840814366707</v>
       </c>
       <c r="D49">
-        <v>581.2393905787571</v>
+        <v>571.9319185633294</v>
       </c>
       <c r="E49">
-        <v>635.5740000000001</v>
+        <v>651.316</v>
       </c>
       <c r="F49">
-        <v>739.874</v>
+        <v>755.6160000000001</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5293,37 +5293,37 @@
         <v>66.024</v>
       </c>
       <c r="M49">
-        <v>174.4622892</v>
+        <v>178.1742528</v>
       </c>
       <c r="N49">
-        <v>-108.4382892</v>
+        <v>-112.1502528</v>
       </c>
       <c r="O49">
-        <v>-34.70025254400001</v>
+        <v>-35.88808089600001</v>
       </c>
       <c r="P49">
-        <v>-73.73803665600001</v>
+        <v>-76.26217190400001</v>
       </c>
       <c r="Q49">
-        <v>-73.562036656</v>
+        <v>-76.08617190400001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1229202248016464</v>
+        <v>0.1244033060478319</v>
       </c>
       <c r="T49">
-        <v>1.005135059407803</v>
+        <v>1.02446457978103</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.1211017011004576</v>
+        <v>0.1185787489941981</v>
       </c>
       <c r="W49">
-        <v>0.2072442188805121</v>
+        <v>0.2078391309871681</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3784428159389301</v>
+        <v>0.370558590606869</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1644525020187133</v>
+        <v>0.1663525020187133</v>
       </c>
       <c r="C50">
-        <v>-183.6840814366703</v>
+        <v>-208.4401676403864</v>
       </c>
       <c r="D50">
-        <v>571.9319185633296</v>
+        <v>562.9178323596136</v>
       </c>
       <c r="E50">
-        <v>651.316</v>
+        <v>667.058</v>
       </c>
       <c r="F50">
-        <v>755.616</v>
+        <v>771.3580000000001</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5375,37 +5375,37 @@
         <v>66.024</v>
       </c>
       <c r="M50">
-        <v>178.1742528</v>
+        <v>181.8862164</v>
       </c>
       <c r="N50">
-        <v>-112.1502528</v>
+        <v>-115.8622164</v>
       </c>
       <c r="O50">
-        <v>-35.88808089600001</v>
+        <v>-37.07590924800001</v>
       </c>
       <c r="P50">
-        <v>-76.262171904</v>
+        <v>-78.78630715200001</v>
       </c>
       <c r="Q50">
-        <v>-76.086171904</v>
+        <v>-78.610307152</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1244033060478318</v>
+        <v>0.1259445473428874</v>
       </c>
       <c r="T50">
-        <v>1.02446457978103</v>
+        <v>1.04455212056105</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.1185787489941981</v>
+        <v>0.1161587745249287</v>
       </c>
       <c r="W50">
-        <v>0.2078391309871681</v>
+        <v>0.2084097609670218</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3705585906068691</v>
+        <v>0.3629961703904023</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1663525020187133</v>
+        <v>0.1682525020187133</v>
       </c>
       <c r="C51">
-        <v>-208.4401676403864</v>
+        <v>-232.9165247490702</v>
       </c>
       <c r="D51">
-        <v>562.9178323596136</v>
+        <v>554.1834752509299</v>
       </c>
       <c r="E51">
-        <v>667.058</v>
+        <v>682.8</v>
       </c>
       <c r="F51">
-        <v>771.3580000000001</v>
+        <v>787.1</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5457,37 +5457,37 @@
         <v>66.024</v>
       </c>
       <c r="M51">
-        <v>181.8862164</v>
+        <v>185.59818</v>
       </c>
       <c r="N51">
-        <v>-115.8622164</v>
+        <v>-119.57418</v>
       </c>
       <c r="O51">
-        <v>-37.07590924800001</v>
+        <v>-38.26373760000001</v>
       </c>
       <c r="P51">
-        <v>-78.78630715200001</v>
+        <v>-81.3104424</v>
       </c>
       <c r="Q51">
-        <v>-78.610307152</v>
+        <v>-81.1344424</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1259445473428874</v>
+        <v>0.1275474382897451</v>
       </c>
       <c r="T51">
-        <v>1.04455212056105</v>
+        <v>1.065443162972271</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.1161587745249287</v>
+        <v>0.1138355990344302</v>
       </c>
       <c r="W51">
-        <v>0.2084097609670218</v>
+        <v>0.2089575657476814</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3629961703904023</v>
+        <v>0.3557362469825943</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1682525020187133</v>
+        <v>0.1701525020187132</v>
       </c>
       <c r="C52">
-        <v>-232.9165247490702</v>
+        <v>-257.1259748275438</v>
       </c>
       <c r="D52">
-        <v>554.1834752509299</v>
+        <v>545.7160251724562</v>
       </c>
       <c r="E52">
-        <v>682.8</v>
+        <v>698.5419999999999</v>
       </c>
       <c r="F52">
-        <v>787.1</v>
+        <v>802.842</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5539,37 +5539,37 @@
         <v>66.024</v>
       </c>
       <c r="M52">
-        <v>185.59818</v>
+        <v>189.3101436</v>
       </c>
       <c r="N52">
-        <v>-119.57418</v>
+        <v>-123.2861436</v>
       </c>
       <c r="O52">
-        <v>-38.26373760000001</v>
+        <v>-39.451565952</v>
       </c>
       <c r="P52">
-        <v>-81.3104424</v>
+        <v>-83.83457764799999</v>
       </c>
       <c r="Q52">
-        <v>-81.1344424</v>
+        <v>-83.65857764799999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1275474382897451</v>
+        <v>0.1292157533568828</v>
       </c>
       <c r="T52">
-        <v>1.065443162972271</v>
+        <v>1.087186900992114</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.1138355990344302</v>
+        <v>0.1116035284651276</v>
       </c>
       <c r="W52">
-        <v>0.2089575657476814</v>
+        <v>0.2094838879879229</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3557362469825943</v>
+        <v>0.3487610264535238</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1701525020187132</v>
+        <v>0.1720525020187132</v>
       </c>
       <c r="C53">
-        <v>-257.1259748275438</v>
+        <v>-281.0805680930143</v>
       </c>
       <c r="D53">
-        <v>545.7160251724562</v>
+        <v>537.5034319069857</v>
       </c>
       <c r="E53">
-        <v>698.5419999999999</v>
+        <v>714.2840000000001</v>
       </c>
       <c r="F53">
-        <v>802.842</v>
+        <v>818.5840000000001</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5621,37 +5621,37 @@
         <v>66.024</v>
       </c>
       <c r="M53">
-        <v>189.3101436</v>
+        <v>193.0221072</v>
       </c>
       <c r="N53">
-        <v>-123.2861436</v>
+        <v>-126.9981072</v>
       </c>
       <c r="O53">
-        <v>-39.451565952</v>
+        <v>-40.63939430400001</v>
       </c>
       <c r="P53">
-        <v>-83.83457764799999</v>
+        <v>-86.35871289600001</v>
       </c>
       <c r="Q53">
-        <v>-83.65857764799999</v>
+        <v>-86.18271289600001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1292157533568828</v>
+        <v>0.1309535815518179</v>
       </c>
       <c r="T53">
-        <v>1.087186900992114</v>
+        <v>1.109836628096116</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.1116035284651276</v>
+        <v>0.1094573067638752</v>
       </c>
       <c r="W53">
-        <v>0.2094838879879229</v>
+        <v>0.2099899670650782</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3487610264535238</v>
+        <v>0.3420540836371099</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1720525020187132</v>
+        <v>0.1739525020187133</v>
       </c>
       <c r="C54">
-        <v>-281.0805680930143</v>
+        <v>-304.7916401324674</v>
       </c>
       <c r="D54">
-        <v>537.5034319069857</v>
+        <v>529.5343598675327</v>
       </c>
       <c r="E54">
-        <v>714.2840000000001</v>
+        <v>730.0260000000001</v>
       </c>
       <c r="F54">
-        <v>818.5840000000001</v>
+        <v>834.326</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5703,37 +5703,37 @@
         <v>66.024</v>
       </c>
       <c r="M54">
-        <v>193.0221072</v>
+        <v>196.7340708</v>
       </c>
       <c r="N54">
-        <v>-126.9981072</v>
+        <v>-130.7100708</v>
       </c>
       <c r="O54">
-        <v>-40.63939430400001</v>
+        <v>-41.827222656</v>
       </c>
       <c r="P54">
-        <v>-86.35871289600001</v>
+        <v>-88.88284814400001</v>
       </c>
       <c r="Q54">
-        <v>-86.18271289600001</v>
+        <v>-88.70684814400001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1309535815518179</v>
+        <v>0.1327653598827076</v>
       </c>
       <c r="T54">
-        <v>1.109836628096116</v>
+        <v>1.133450173374757</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.1094573067638752</v>
+        <v>0.1073920745607832</v>
       </c>
       <c r="W54">
-        <v>0.2099899670650782</v>
+        <v>0.2104769488185673</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3420540836371099</v>
+        <v>0.3356002330024475</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1739525020187133</v>
+        <v>0.1758525020187132</v>
       </c>
       <c r="C55">
-        <v>-304.7916401324674</v>
+        <v>-328.269864104564</v>
       </c>
       <c r="D55">
-        <v>529.5343598675327</v>
+        <v>521.7981358954361</v>
       </c>
       <c r="E55">
-        <v>730.0260000000001</v>
+        <v>745.768</v>
       </c>
       <c r="F55">
-        <v>834.326</v>
+        <v>850.0680000000001</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5785,37 +5785,37 @@
         <v>66.024</v>
       </c>
       <c r="M55">
-        <v>196.7340708</v>
+        <v>200.4460344</v>
       </c>
       <c r="N55">
-        <v>-130.7100708</v>
+        <v>-134.4220344</v>
       </c>
       <c r="O55">
-        <v>-41.827222656</v>
+        <v>-43.01505100800001</v>
       </c>
       <c r="P55">
-        <v>-88.88284814400001</v>
+        <v>-91.40698339200003</v>
       </c>
       <c r="Q55">
-        <v>-88.70684814400001</v>
+        <v>-91.23098339200003</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1327653598827076</v>
+        <v>0.1346559111845056</v>
       </c>
       <c r="T55">
-        <v>1.133450173374757</v>
+        <v>1.158090394535078</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.1073920745607832</v>
+        <v>0.1054033324392872</v>
       </c>
       <c r="W55">
-        <v>0.2104769488185673</v>
+        <v>0.2109458942108161</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3356002330024475</v>
+        <v>0.3293854138727725</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1758525020187132</v>
+        <v>0.1777525020187133</v>
       </c>
       <c r="C56">
-        <v>-328.269864104564</v>
+        <v>-351.525298431567</v>
       </c>
       <c r="D56">
-        <v>521.7981358954361</v>
+        <v>514.2847015684331</v>
       </c>
       <c r="E56">
-        <v>745.768</v>
+        <v>761.51</v>
       </c>
       <c r="F56">
-        <v>850.0680000000001</v>
+        <v>865.8100000000001</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5867,37 +5867,37 @@
         <v>66.024</v>
       </c>
       <c r="M56">
-        <v>200.4460344</v>
+        <v>204.157998</v>
       </c>
       <c r="N56">
-        <v>-134.4220344</v>
+        <v>-138.133998</v>
       </c>
       <c r="O56">
-        <v>-43.01505100800001</v>
+        <v>-44.20287936</v>
       </c>
       <c r="P56">
-        <v>-91.40698339200003</v>
+        <v>-93.93111864000002</v>
       </c>
       <c r="Q56">
-        <v>-91.23098339200003</v>
+        <v>-93.75511864000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1346559111845056</v>
+        <v>0.1366304869886057</v>
       </c>
       <c r="T56">
-        <v>1.158090394535078</v>
+        <v>1.183825736635857</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.1054033324392872</v>
+        <v>0.1034869082131183</v>
       </c>
       <c r="W56">
-        <v>0.2109458942108161</v>
+        <v>0.2113977870433467</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3293854138727725</v>
+        <v>0.3233965881659948</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1777525020187133</v>
+        <v>0.1796525020187132</v>
       </c>
       <c r="C57">
-        <v>-351.525298431567</v>
+        <v>-374.567430429424</v>
       </c>
       <c r="D57">
-        <v>514.2847015684331</v>
+        <v>506.9845695705761</v>
       </c>
       <c r="E57">
-        <v>761.51</v>
+        <v>777.2520000000002</v>
       </c>
       <c r="F57">
-        <v>865.8100000000001</v>
+        <v>881.5520000000001</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5949,37 +5949,37 @@
         <v>66.024</v>
       </c>
       <c r="M57">
-        <v>204.157998</v>
+        <v>207.8699616</v>
       </c>
       <c r="N57">
-        <v>-138.133998</v>
+        <v>-141.8459616</v>
       </c>
       <c r="O57">
-        <v>-44.20287936</v>
+        <v>-45.39070771200002</v>
       </c>
       <c r="P57">
-        <v>-93.93111864000002</v>
+        <v>-96.45525388800002</v>
       </c>
       <c r="Q57">
-        <v>-93.75511864000002</v>
+        <v>-96.27925388800001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1366304869886057</v>
+        <v>0.1386948162383467</v>
       </c>
       <c r="T57">
-        <v>1.183825736635857</v>
+        <v>1.210730867013945</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.1034869082131183</v>
+        <v>0.1016389277093126</v>
       </c>
       <c r="W57">
-        <v>0.2113977870433467</v>
+        <v>0.2118335408461441</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3233965881659948</v>
+        <v>0.3176216490916021</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1796525020187132</v>
+        <v>0.1815525020187133</v>
       </c>
       <c r="C58">
-        <v>-374.567430429424</v>
+        <v>-397.4052162739554</v>
       </c>
       <c r="D58">
-        <v>506.9845695705761</v>
+        <v>499.8887837260447</v>
       </c>
       <c r="E58">
-        <v>777.2520000000002</v>
+        <v>792.9940000000001</v>
       </c>
       <c r="F58">
-        <v>881.5520000000001</v>
+        <v>897.2940000000001</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6031,37 +6031,37 @@
         <v>66.024</v>
       </c>
       <c r="M58">
-        <v>207.8699616</v>
+        <v>211.5819252</v>
       </c>
       <c r="N58">
-        <v>-141.8459616</v>
+        <v>-145.5579252</v>
       </c>
       <c r="O58">
-        <v>-45.39070771200002</v>
+        <v>-46.57853606400001</v>
       </c>
       <c r="P58">
-        <v>-96.45525388800002</v>
+        <v>-98.97938913600001</v>
       </c>
       <c r="Q58">
-        <v>-96.27925388800001</v>
+        <v>-98.80338913600001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1386948162383467</v>
+        <v>0.1408551608020292</v>
       </c>
       <c r="T58">
-        <v>1.210730867013945</v>
+        <v>1.238887398804967</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1016389277093126</v>
+        <v>0.09985578862669314</v>
       </c>
       <c r="W58">
-        <v>0.2118335408461441</v>
+        <v>0.2122540050418258</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3176216490916021</v>
+        <v>0.3120493394584161</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1815525020187133</v>
+        <v>0.1834525020187132</v>
       </c>
       <c r="C59">
-        <v>-397.4052162739554</v>
+        <v>-420.0471176571525</v>
       </c>
       <c r="D59">
-        <v>499.8887837260447</v>
+        <v>492.9888823428477</v>
       </c>
       <c r="E59">
-        <v>792.9940000000001</v>
+        <v>808.7360000000001</v>
       </c>
       <c r="F59">
-        <v>897.2940000000001</v>
+        <v>913.0360000000002</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6113,37 +6113,37 @@
         <v>66.024</v>
       </c>
       <c r="M59">
-        <v>211.5819252</v>
+        <v>215.2938888</v>
       </c>
       <c r="N59">
-        <v>-145.5579252</v>
+        <v>-149.2698888</v>
       </c>
       <c r="O59">
-        <v>-46.57853606400001</v>
+        <v>-47.76636441600002</v>
       </c>
       <c r="P59">
-        <v>-98.97938913600001</v>
+        <v>-101.503524384</v>
       </c>
       <c r="Q59">
-        <v>-98.80338913600001</v>
+        <v>-101.327524384</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1408551608020292</v>
+        <v>0.1431183789163633</v>
       </c>
       <c r="T59">
-        <v>1.238887398804967</v>
+        <v>1.268384717824133</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.09985578862669314</v>
+        <v>0.0981341370986467</v>
       </c>
       <c r="W59">
-        <v>0.2122540050418258</v>
+        <v>0.2126599704721391</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3120493394584161</v>
+        <v>0.3066691784332709</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1834525020187132</v>
+        <v>0.1853525020187132</v>
       </c>
       <c r="C60">
-        <v>-420.0471176571523</v>
+        <v>-442.5011354490355</v>
       </c>
       <c r="D60">
-        <v>492.9888823428477</v>
+        <v>486.2768645509645</v>
       </c>
       <c r="E60">
-        <v>808.7359999999999</v>
+        <v>824.4780000000001</v>
       </c>
       <c r="F60">
-        <v>913.0359999999999</v>
+        <v>928.778</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6195,37 +6195,37 @@
         <v>66.024</v>
       </c>
       <c r="M60">
-        <v>215.2938888</v>
+        <v>219.0058524</v>
       </c>
       <c r="N60">
-        <v>-149.2698888</v>
+        <v>-152.9818524</v>
       </c>
       <c r="O60">
-        <v>-47.76636441599999</v>
+        <v>-48.95419276800001</v>
       </c>
       <c r="P60">
-        <v>-101.503524384</v>
+        <v>-104.027659632</v>
       </c>
       <c r="Q60">
-        <v>-101.327524384</v>
+        <v>-103.851659632</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1431183789163633</v>
+        <v>0.1454919979143233</v>
       </c>
       <c r="T60">
-        <v>1.268384717824133</v>
+        <v>1.299320930453989</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.09813413709864673</v>
+        <v>0.09647084663934762</v>
       </c>
       <c r="W60">
-        <v>0.2126599704721391</v>
+        <v>0.2130521743624418</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.306669178433271</v>
+        <v>0.3014713957479613</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1853525020187132</v>
+        <v>0.1872525020187132</v>
       </c>
       <c r="C61">
-        <v>-442.5011354490355</v>
+        <v>-464.7748406466191</v>
       </c>
       <c r="D61">
-        <v>486.2768645509645</v>
+        <v>479.7451593533809</v>
       </c>
       <c r="E61">
-        <v>824.4780000000001</v>
+        <v>840.22</v>
       </c>
       <c r="F61">
-        <v>928.778</v>
+        <v>944.52</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6277,37 +6277,37 @@
         <v>66.024</v>
       </c>
       <c r="M61">
-        <v>219.0058524</v>
+        <v>222.717816</v>
       </c>
       <c r="N61">
-        <v>-152.9818524</v>
+        <v>-156.693816</v>
       </c>
       <c r="O61">
-        <v>-48.95419276800001</v>
+        <v>-50.14202112</v>
       </c>
       <c r="P61">
-        <v>-104.027659632</v>
+        <v>-106.55179488</v>
       </c>
       <c r="Q61">
-        <v>-103.851659632</v>
+        <v>-106.37579488</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1454919979143233</v>
+        <v>0.1479842978621814</v>
       </c>
       <c r="T61">
-        <v>1.299320930453989</v>
+        <v>1.331803953715339</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.09647084663934762</v>
+        <v>0.0948629991953585</v>
       </c>
       <c r="W61">
-        <v>0.2130521743624418</v>
+        <v>0.2134313047897345</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3014713957479613</v>
+        <v>0.2964468724854953</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1872525020187132</v>
+        <v>0.1891525020187133</v>
       </c>
       <c r="C62">
-        <v>-464.7748406466191</v>
+        <v>-486.8754028616856</v>
       </c>
       <c r="D62">
-        <v>479.7451593533809</v>
+        <v>473.3865971383144</v>
       </c>
       <c r="E62">
-        <v>840.22</v>
+        <v>855.962</v>
       </c>
       <c r="F62">
-        <v>944.52</v>
+        <v>960.2620000000001</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6359,37 +6359,37 @@
         <v>66.024</v>
       </c>
       <c r="M62">
-        <v>222.717816</v>
+        <v>226.4297796</v>
       </c>
       <c r="N62">
-        <v>-156.693816</v>
+        <v>-160.4057796</v>
       </c>
       <c r="O62">
-        <v>-50.14202112</v>
+        <v>-51.32984947200001</v>
       </c>
       <c r="P62">
-        <v>-106.55179488</v>
+        <v>-109.075930128</v>
       </c>
       <c r="Q62">
-        <v>-106.37579488</v>
+        <v>-108.899930128</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1479842978621814</v>
+        <v>0.1506044080637758</v>
       </c>
       <c r="T62">
-        <v>1.331803953715339</v>
+        <v>1.365952773041374</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0948629991953585</v>
+        <v>0.09330786806100834</v>
       </c>
       <c r="W62">
-        <v>0.2134313047897345</v>
+        <v>0.2137980047112142</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2964468724854953</v>
+        <v>0.2915870876906511</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1891525020187133</v>
+        <v>0.1910525020187133</v>
       </c>
       <c r="C63">
-        <v>-486.8754028616856</v>
+        <v>-508.8096165727233</v>
       </c>
       <c r="D63">
-        <v>473.3865971383144</v>
+        <v>467.1943834272768</v>
       </c>
       <c r="E63">
-        <v>855.962</v>
+        <v>871.704</v>
       </c>
       <c r="F63">
-        <v>960.2620000000001</v>
+        <v>976.004</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6441,37 +6441,37 @@
         <v>66.024</v>
       </c>
       <c r="M63">
-        <v>226.4297796</v>
+        <v>230.1417432</v>
       </c>
       <c r="N63">
-        <v>-160.4057796</v>
+        <v>-164.1177432</v>
       </c>
       <c r="O63">
-        <v>-51.32984947200001</v>
+        <v>-52.517677824</v>
       </c>
       <c r="P63">
-        <v>-109.075930128</v>
+        <v>-111.600065376</v>
       </c>
       <c r="Q63">
-        <v>-108.899930128</v>
+        <v>-111.424065376</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1506044080637758</v>
+        <v>0.1533624188022962</v>
       </c>
       <c r="T63">
-        <v>1.365952773041374</v>
+        <v>1.401898898647725</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.09330786806100834</v>
+        <v>0.09180290244712111</v>
       </c>
       <c r="W63">
-        <v>0.2137980047112142</v>
+        <v>0.2141528756029689</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2915870876906511</v>
+        <v>0.2868840701472535</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1910525020187133</v>
+        <v>0.1929525020187133</v>
       </c>
       <c r="C64">
-        <v>-508.8096165727233</v>
+        <v>-530.5839253431099</v>
       </c>
       <c r="D64">
-        <v>467.1943834272768</v>
+        <v>461.1620746568901</v>
       </c>
       <c r="E64">
-        <v>871.704</v>
+        <v>887.4459999999999</v>
       </c>
       <c r="F64">
-        <v>976.004</v>
+        <v>991.746</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6523,37 +6523,37 @@
         <v>66.024</v>
       </c>
       <c r="M64">
-        <v>230.1417432</v>
+        <v>233.8537068</v>
       </c>
       <c r="N64">
-        <v>-164.1177432</v>
+        <v>-167.8297068</v>
       </c>
       <c r="O64">
-        <v>-52.517677824</v>
+        <v>-53.705506176</v>
       </c>
       <c r="P64">
-        <v>-111.600065376</v>
+        <v>-114.124200624</v>
       </c>
       <c r="Q64">
-        <v>-111.424065376</v>
+        <v>-113.948200624</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1533624188022962</v>
+        <v>0.1562695112023583</v>
       </c>
       <c r="T64">
-        <v>1.401898898647725</v>
+        <v>1.439788058070637</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.09180290244712111</v>
+        <v>0.09034571351938904</v>
       </c>
       <c r="W64">
-        <v>0.2141528756029689</v>
+        <v>0.2144964807521281</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2868840701472535</v>
+        <v>0.2823303547480908</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1929525020187133</v>
+        <v>0.1948525020187133</v>
       </c>
       <c r="C65">
-        <v>-530.5839253431099</v>
+        <v>-552.2044441870144</v>
       </c>
       <c r="D65">
-        <v>461.1620746568901</v>
+        <v>455.2835558129857</v>
       </c>
       <c r="E65">
-        <v>887.4459999999999</v>
+        <v>903.1880000000001</v>
       </c>
       <c r="F65">
-        <v>991.746</v>
+        <v>1007.488</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6605,37 +6605,37 @@
         <v>66.024</v>
       </c>
       <c r="M65">
-        <v>233.8537068</v>
+        <v>237.5656704</v>
       </c>
       <c r="N65">
-        <v>-167.8297068</v>
+        <v>-171.5416704</v>
       </c>
       <c r="O65">
-        <v>-53.705506176</v>
+        <v>-54.893334528</v>
       </c>
       <c r="P65">
-        <v>-114.124200624</v>
+        <v>-116.648335872</v>
       </c>
       <c r="Q65">
-        <v>-113.948200624</v>
+        <v>-116.472335872</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1562695112023583</v>
+        <v>0.1593381087357571</v>
       </c>
       <c r="T65">
-        <v>1.439788058070637</v>
+        <v>1.479782170794822</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.09034571351938904</v>
+        <v>0.08893406174564858</v>
       </c>
       <c r="W65">
-        <v>0.2144964807521281</v>
+        <v>0.2148293482403761</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2823303547480908</v>
+        <v>0.2779189429551518</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1948525020187133</v>
+        <v>0.1967525020187132</v>
       </c>
       <c r="C66">
-        <v>-552.2044441870144</v>
+        <v>-573.676980246214</v>
       </c>
       <c r="D66">
-        <v>455.2835558129857</v>
+        <v>449.553019753786</v>
       </c>
       <c r="E66">
-        <v>903.1880000000001</v>
+        <v>918.9300000000001</v>
       </c>
       <c r="F66">
-        <v>1007.488</v>
+        <v>1023.23</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6687,37 +6687,37 @@
         <v>66.024</v>
       </c>
       <c r="M66">
-        <v>237.5656704</v>
+        <v>241.277634</v>
       </c>
       <c r="N66">
-        <v>-171.5416704</v>
+        <v>-175.253634</v>
       </c>
       <c r="O66">
-        <v>-54.893334528</v>
+        <v>-56.08116288</v>
       </c>
       <c r="P66">
-        <v>-116.648335872</v>
+        <v>-119.17247112</v>
       </c>
       <c r="Q66">
-        <v>-116.472335872</v>
+        <v>-118.99647112</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1593381087357571</v>
+        <v>0.1625820546996359</v>
       </c>
       <c r="T66">
-        <v>1.479782170794822</v>
+        <v>1.522061661388959</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.08893406174564858</v>
+        <v>0.08756584541110014</v>
       </c>
       <c r="W66">
-        <v>0.2148293482403761</v>
+        <v>0.2151519736520626</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2779189429551518</v>
+        <v>0.273643266909688</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1967525020187132</v>
+        <v>0.1986525020187132</v>
       </c>
       <c r="C67">
-        <v>-573.676980246214</v>
+        <v>-595.0070519248027</v>
       </c>
       <c r="D67">
-        <v>449.553019753786</v>
+        <v>443.9649480751973</v>
       </c>
       <c r="E67">
-        <v>918.9300000000001</v>
+        <v>934.672</v>
       </c>
       <c r="F67">
-        <v>1023.23</v>
+        <v>1038.972</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6769,37 +6769,37 @@
         <v>66.024</v>
       </c>
       <c r="M67">
-        <v>241.277634</v>
+        <v>244.9895976</v>
       </c>
       <c r="N67">
-        <v>-175.253634</v>
+        <v>-178.9655976</v>
       </c>
       <c r="O67">
-        <v>-56.08116288</v>
+        <v>-57.268991232</v>
       </c>
       <c r="P67">
-        <v>-119.17247112</v>
+        <v>-121.696606368</v>
       </c>
       <c r="Q67">
-        <v>-118.99647112</v>
+        <v>-121.520606368</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1625820546996359</v>
+        <v>0.1660168210143311</v>
       </c>
       <c r="T67">
-        <v>1.522061661388959</v>
+        <v>1.566828180841576</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.08756584541110014</v>
+        <v>0.08623909017759862</v>
       </c>
       <c r="W67">
-        <v>0.2151519736520626</v>
+        <v>0.2154648225361222</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.273643266909688</v>
+        <v>0.2694971568049958</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1986525020187132</v>
+        <v>0.2005525020187133</v>
       </c>
       <c r="C68">
-        <v>-595.0070519248027</v>
+        <v>-616.199906614318</v>
       </c>
       <c r="D68">
-        <v>443.9649480751973</v>
+        <v>438.5140933856822</v>
       </c>
       <c r="E68">
-        <v>934.672</v>
+        <v>950.4140000000002</v>
       </c>
       <c r="F68">
-        <v>1038.972</v>
+        <v>1054.714</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6851,37 +6851,37 @@
         <v>66.024</v>
       </c>
       <c r="M68">
-        <v>244.9895976</v>
+        <v>248.7015612</v>
       </c>
       <c r="N68">
-        <v>-178.9655976</v>
+        <v>-182.6775612</v>
       </c>
       <c r="O68">
-        <v>-57.268991232</v>
+        <v>-58.45681958400002</v>
       </c>
       <c r="P68">
-        <v>-121.696606368</v>
+        <v>-124.220741616</v>
       </c>
       <c r="Q68">
-        <v>-121.520606368</v>
+        <v>-124.044741616</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1660168210143311</v>
+        <v>0.1696597549844623</v>
       </c>
       <c r="T68">
-        <v>1.566828180841576</v>
+        <v>1.61430782268526</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.08623909017759862</v>
+        <v>0.08495193957793296</v>
       </c>
       <c r="W68">
-        <v>0.2154648225361222</v>
+        <v>0.2157683326475234</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2694971568049958</v>
+        <v>0.2654748111810405</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2005525020187133</v>
+        <v>0.2024525020187133</v>
       </c>
       <c r="C69">
-        <v>-616.199906614318</v>
+        <v>-637.2605371289667</v>
       </c>
       <c r="D69">
-        <v>438.5140933856822</v>
+        <v>433.1954628710335</v>
       </c>
       <c r="E69">
-        <v>950.4140000000002</v>
+        <v>966.1560000000002</v>
       </c>
       <c r="F69">
-        <v>1054.714</v>
+        <v>1070.456</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6933,37 +6933,37 @@
         <v>66.024</v>
       </c>
       <c r="M69">
-        <v>248.7015612</v>
+        <v>252.4135248</v>
       </c>
       <c r="N69">
-        <v>-182.6775612</v>
+        <v>-186.3895248</v>
       </c>
       <c r="O69">
-        <v>-58.45681958400002</v>
+        <v>-59.64464793600001</v>
       </c>
       <c r="P69">
-        <v>-124.220741616</v>
+        <v>-126.744876864</v>
       </c>
       <c r="Q69">
-        <v>-124.044741616</v>
+        <v>-126.568876864</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1696597549844623</v>
+        <v>0.1735303723277268</v>
       </c>
       <c r="T69">
-        <v>1.61430782268526</v>
+        <v>1.664754942144175</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.08495193957793296</v>
+        <v>0.08370264634884572</v>
       </c>
       <c r="W69">
-        <v>0.2157683326475234</v>
+        <v>0.2160629159909422</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2654748111810405</v>
+        <v>0.2615707698401428</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2024525020187133</v>
+        <v>0.2043525020187133</v>
       </c>
       <c r="C70">
-        <v>-637.2605371289667</v>
+        <v>-658.1936969591522</v>
       </c>
       <c r="D70">
-        <v>433.1954628710335</v>
+        <v>428.0043030408479</v>
       </c>
       <c r="E70">
-        <v>966.1560000000002</v>
+        <v>981.8980000000001</v>
       </c>
       <c r="F70">
-        <v>1070.456</v>
+        <v>1086.198</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7015,37 +7015,37 @@
         <v>66.024</v>
       </c>
       <c r="M70">
-        <v>252.4135248</v>
+        <v>256.1254884000001</v>
       </c>
       <c r="N70">
-        <v>-186.3895248</v>
+        <v>-190.1014884000001</v>
       </c>
       <c r="O70">
-        <v>-59.64464793600001</v>
+        <v>-60.83247628800002</v>
       </c>
       <c r="P70">
-        <v>-126.744876864</v>
+        <v>-129.269012112</v>
       </c>
       <c r="Q70">
-        <v>-126.568876864</v>
+        <v>-129.0930121120001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1735303723277268</v>
+        <v>0.1776507069189438</v>
       </c>
       <c r="T70">
-        <v>1.664754942144175</v>
+        <v>1.718456714471406</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.08370264634884572</v>
+        <v>0.08248956451770303</v>
       </c>
       <c r="W70">
-        <v>0.2160629159909422</v>
+        <v>0.2163489606867256</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2615707698401428</v>
+        <v>0.2577798891178219</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2043525020187133</v>
+        <v>0.2062525020187133</v>
       </c>
       <c r="C71">
-        <v>-658.1936969591522</v>
+        <v>-679.0039144412501</v>
       </c>
       <c r="D71">
-        <v>428.0043030408479</v>
+        <v>422.93608555875</v>
       </c>
       <c r="E71">
-        <v>981.8980000000001</v>
+        <v>997.6400000000001</v>
       </c>
       <c r="F71">
-        <v>1086.198</v>
+        <v>1101.94</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7097,37 +7097,37 @@
         <v>66.024</v>
       </c>
       <c r="M71">
-        <v>256.1254884000001</v>
+        <v>259.837452</v>
       </c>
       <c r="N71">
-        <v>-190.1014884000001</v>
+        <v>-193.813452</v>
       </c>
       <c r="O71">
-        <v>-60.83247628800002</v>
+        <v>-62.02030464000001</v>
       </c>
       <c r="P71">
-        <v>-129.269012112</v>
+        <v>-131.79314736</v>
       </c>
       <c r="Q71">
-        <v>-129.0930121120001</v>
+        <v>-131.61714736</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1776507069189438</v>
+        <v>0.1820457304829086</v>
       </c>
       <c r="T71">
-        <v>1.718456714471406</v>
+        <v>1.775738604953786</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.08248956451770303</v>
+        <v>0.08131114216745011</v>
       </c>
       <c r="W71">
-        <v>0.2163489606867256</v>
+        <v>0.2166268326769153</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2577798891178219</v>
+        <v>0.2540973192732816</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2062525020187133</v>
+        <v>0.2081525020187133</v>
       </c>
       <c r="C72">
-        <v>-679.0039144412501</v>
+        <v>-699.6955059324182</v>
       </c>
       <c r="D72">
-        <v>422.93608555875</v>
+        <v>417.986494067582</v>
       </c>
       <c r="E72">
-        <v>997.6400000000001</v>
+        <v>1013.382</v>
       </c>
       <c r="F72">
-        <v>1101.94</v>
+        <v>1117.682</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7179,37 +7179,37 @@
         <v>66.024</v>
       </c>
       <c r="M72">
-        <v>259.837452</v>
+        <v>263.5494156000001</v>
       </c>
       <c r="N72">
-        <v>-193.813452</v>
+        <v>-197.5254156000001</v>
       </c>
       <c r="O72">
-        <v>-62.02030464000001</v>
+        <v>-63.20813299200003</v>
       </c>
       <c r="P72">
-        <v>-131.79314736</v>
+        <v>-134.3172826080001</v>
       </c>
       <c r="Q72">
-        <v>-131.61714736</v>
+        <v>-134.1412826080001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1820457304829086</v>
+        <v>0.1867438591202503</v>
       </c>
       <c r="T72">
-        <v>1.775738604953786</v>
+        <v>1.836970970641848</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08131114216745011</v>
+        <v>0.08016591481297898</v>
       </c>
       <c r="W72">
-        <v>0.2166268326769153</v>
+        <v>0.2168968772870996</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2540973192732816</v>
+        <v>0.2505184837905593</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2081525020187133</v>
+        <v>0.2100525020187132</v>
       </c>
       <c r="C73">
-        <v>-699.695505932418</v>
+        <v>-720.2725880710016</v>
       </c>
       <c r="D73">
-        <v>417.986494067582</v>
+        <v>413.1514119289984</v>
       </c>
       <c r="E73">
-        <v>1013.382</v>
+        <v>1029.124</v>
       </c>
       <c r="F73">
-        <v>1117.682</v>
+        <v>1133.424</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7261,37 +7261,37 @@
         <v>66.024</v>
       </c>
       <c r="M73">
-        <v>263.5494156</v>
+        <v>267.2613792</v>
       </c>
       <c r="N73">
-        <v>-197.5254156</v>
+        <v>-201.2373792</v>
       </c>
       <c r="O73">
-        <v>-63.20813299200001</v>
+        <v>-64.39596134400001</v>
       </c>
       <c r="P73">
-        <v>-134.317282608</v>
+        <v>-136.841417856</v>
       </c>
       <c r="Q73">
-        <v>-134.141282608</v>
+        <v>-136.665417856</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1867438591202502</v>
+        <v>0.1917775683745449</v>
       </c>
       <c r="T73">
-        <v>1.836970970641847</v>
+        <v>1.902577076736199</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08016591481297899</v>
+        <v>0.0790524993294654</v>
       </c>
       <c r="W73">
-        <v>0.2168968772870996</v>
+        <v>0.2171594206581121</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2505184837905594</v>
+        <v>0.2470390604045793</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2100525020187132</v>
+        <v>0.2119525020187133</v>
       </c>
       <c r="C74">
-        <v>-720.2725880710016</v>
+        <v>-740.7390891957377</v>
       </c>
       <c r="D74">
-        <v>413.1514119289984</v>
+        <v>408.4269108042623</v>
       </c>
       <c r="E74">
-        <v>1029.124</v>
+        <v>1044.866</v>
       </c>
       <c r="F74">
-        <v>1133.424</v>
+        <v>1149.166</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7343,37 +7343,37 @@
         <v>66.024</v>
       </c>
       <c r="M74">
-        <v>267.2613792</v>
+        <v>270.9733428</v>
       </c>
       <c r="N74">
-        <v>-201.2373792</v>
+        <v>-204.9493428</v>
       </c>
       <c r="O74">
-        <v>-64.39596134400001</v>
+        <v>-65.58378969600001</v>
       </c>
       <c r="P74">
-        <v>-136.841417856</v>
+        <v>-139.365553104</v>
       </c>
       <c r="Q74">
-        <v>-136.665417856</v>
+        <v>-139.189553104</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1917775683745449</v>
+        <v>0.1971841449810095</v>
       </c>
       <c r="T74">
-        <v>1.902577076736199</v>
+        <v>1.973042894393095</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0790524993294654</v>
+        <v>0.0779695883797467</v>
       </c>
       <c r="W74">
-        <v>0.2171594206581121</v>
+        <v>0.2174147710600557</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2470390604045793</v>
+        <v>0.2436549636867085</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2119525020187133</v>
+        <v>0.2138525020187132</v>
       </c>
       <c r="C75">
-        <v>-740.7390891957377</v>
+        <v>-761.0987599903189</v>
       </c>
       <c r="D75">
-        <v>408.4269108042623</v>
+        <v>403.8092400096813</v>
       </c>
       <c r="E75">
-        <v>1044.866</v>
+        <v>1060.608</v>
       </c>
       <c r="F75">
-        <v>1149.166</v>
+        <v>1164.908</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7425,37 +7425,37 @@
         <v>66.024</v>
       </c>
       <c r="M75">
-        <v>270.9733428</v>
+        <v>274.6853064000001</v>
       </c>
       <c r="N75">
-        <v>-204.9493428</v>
+        <v>-208.6613064000001</v>
       </c>
       <c r="O75">
-        <v>-65.58378969600001</v>
+        <v>-66.77161804800002</v>
       </c>
       <c r="P75">
-        <v>-139.365553104</v>
+        <v>-141.889688352</v>
       </c>
       <c r="Q75">
-        <v>-139.189553104</v>
+        <v>-141.713688352</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1971841449810095</v>
+        <v>0.2030066120956637</v>
       </c>
       <c r="T75">
-        <v>1.973042894393095</v>
+        <v>2.04892915956206</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.0779695883797467</v>
+        <v>0.0769159452935339</v>
       </c>
       <c r="W75">
-        <v>0.2174147710600557</v>
+        <v>0.2176632200997847</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2436549636867085</v>
+        <v>0.2403623290422934</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2138525020187132</v>
+        <v>0.2157525020187133</v>
       </c>
       <c r="C76">
-        <v>-761.0987599903189</v>
+        <v>-781.3551834139524</v>
       </c>
       <c r="D76">
-        <v>403.8092400096813</v>
+        <v>399.2948165860477</v>
       </c>
       <c r="E76">
-        <v>1060.608</v>
+        <v>1076.35</v>
       </c>
       <c r="F76">
-        <v>1164.908</v>
+        <v>1180.65</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7507,37 +7507,37 @@
         <v>66.024</v>
       </c>
       <c r="M76">
-        <v>274.6853064000001</v>
+        <v>278.39727</v>
       </c>
       <c r="N76">
-        <v>-208.6613064000001</v>
+        <v>-212.37327</v>
       </c>
       <c r="O76">
-        <v>-66.77161804800002</v>
+        <v>-67.95944640000002</v>
       </c>
       <c r="P76">
-        <v>-141.889688352</v>
+        <v>-144.4138236</v>
       </c>
       <c r="Q76">
-        <v>-141.713688352</v>
+        <v>-144.2378236</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2030066120956637</v>
+        <v>0.2092948765794903</v>
       </c>
       <c r="T76">
-        <v>2.04892915956206</v>
+        <v>2.130886325944543</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0769159452935339</v>
+        <v>0.07589039935628679</v>
       </c>
       <c r="W76">
-        <v>0.2176632200997847</v>
+        <v>0.2179050438317876</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2403623290422934</v>
+        <v>0.2371574979883961</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2157525020187133</v>
+        <v>0.2176525020187133</v>
       </c>
       <c r="C77">
-        <v>-781.3551834139524</v>
+        <v>-801.5117839731627</v>
       </c>
       <c r="D77">
-        <v>399.2948165860477</v>
+        <v>394.8802160268374</v>
       </c>
       <c r="E77">
-        <v>1076.35</v>
+        <v>1092.092</v>
       </c>
       <c r="F77">
-        <v>1180.65</v>
+        <v>1196.392</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7589,37 +7589,37 @@
         <v>66.024</v>
       </c>
       <c r="M77">
-        <v>278.39727</v>
+        <v>282.1092336</v>
       </c>
       <c r="N77">
-        <v>-212.37327</v>
+        <v>-216.0852336</v>
       </c>
       <c r="O77">
-        <v>-67.95944640000002</v>
+        <v>-69.14727475200002</v>
       </c>
       <c r="P77">
-        <v>-144.4138236</v>
+        <v>-146.937958848</v>
       </c>
       <c r="Q77">
-        <v>-144.2378236</v>
+        <v>-146.761958848</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2092948765794903</v>
+        <v>0.2161071631036357</v>
       </c>
       <c r="T77">
-        <v>2.130886325944543</v>
+        <v>2.219673256192232</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07589039935628679</v>
+        <v>0.07489184147001984</v>
       </c>
       <c r="W77">
-        <v>0.2179050438317876</v>
+        <v>0.2181405037813693</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2371574979883961</v>
+        <v>0.234037004593812</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2176525020187133</v>
+        <v>0.2195525020187132</v>
       </c>
       <c r="C78">
-        <v>-801.5117839731627</v>
+        <v>-821.5718363852664</v>
       </c>
       <c r="D78">
-        <v>394.8802160268374</v>
+        <v>390.5621636147337</v>
       </c>
       <c r="E78">
-        <v>1092.092</v>
+        <v>1107.834</v>
       </c>
       <c r="F78">
-        <v>1196.392</v>
+        <v>1212.134</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7671,37 +7671,37 @@
         <v>66.024</v>
       </c>
       <c r="M78">
-        <v>282.1092336</v>
+        <v>285.8211972</v>
       </c>
       <c r="N78">
-        <v>-216.0852336</v>
+        <v>-219.7971972</v>
       </c>
       <c r="O78">
-        <v>-69.14727475200002</v>
+        <v>-70.33510310400001</v>
       </c>
       <c r="P78">
-        <v>-146.937958848</v>
+        <v>-149.462094096</v>
       </c>
       <c r="Q78">
-        <v>-146.761958848</v>
+        <v>-149.286094096</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2161071631036357</v>
+        <v>0.2235118223690112</v>
       </c>
       <c r="T78">
-        <v>2.219673256192232</v>
+        <v>2.316180789070155</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07489184147001984</v>
+        <v>0.07391922015222739</v>
       </c>
       <c r="W78">
-        <v>0.2181405037813693</v>
+        <v>0.2183698478881048</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.234037004593812</v>
+        <v>0.2309975629757106</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2195525020187132</v>
+        <v>0.2214525020187132</v>
       </c>
       <c r="C79">
-        <v>-821.5718363852664</v>
+        <v>-841.5384736795813</v>
       </c>
       <c r="D79">
-        <v>390.5621636147337</v>
+        <v>386.3375263204186</v>
       </c>
       <c r="E79">
-        <v>1107.834</v>
+        <v>1123.576</v>
       </c>
       <c r="F79">
-        <v>1212.134</v>
+        <v>1227.876</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7753,37 +7753,37 @@
         <v>66.024</v>
       </c>
       <c r="M79">
-        <v>285.8211972</v>
+        <v>289.5331608</v>
       </c>
       <c r="N79">
-        <v>-219.7971972</v>
+        <v>-223.5091608</v>
       </c>
       <c r="O79">
-        <v>-70.33510310400001</v>
+        <v>-71.52293145600001</v>
       </c>
       <c r="P79">
-        <v>-149.462094096</v>
+        <v>-151.986229344</v>
       </c>
       <c r="Q79">
-        <v>-149.286094096</v>
+        <v>-151.810229344</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2235118223690112</v>
+        <v>0.2315896324766935</v>
       </c>
       <c r="T79">
-        <v>2.316180789070155</v>
+        <v>2.421461734027889</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07391922015222739</v>
+        <v>0.07297153784258345</v>
       </c>
       <c r="W79">
-        <v>0.2183698478881048</v>
+        <v>0.2185933113767188</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2309975629757106</v>
+        <v>0.2280360557580733</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2214525020187132</v>
+        <v>0.2233525020187133</v>
       </c>
       <c r="C80">
-        <v>-841.5384736795813</v>
+        <v>-861.4146947784845</v>
       </c>
       <c r="D80">
-        <v>386.3375263204186</v>
+        <v>382.2033052215156</v>
       </c>
       <c r="E80">
-        <v>1123.576</v>
+        <v>1139.318</v>
       </c>
       <c r="F80">
-        <v>1227.876</v>
+        <v>1243.618</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7835,37 +7835,37 @@
         <v>66.024</v>
       </c>
       <c r="M80">
-        <v>289.5331608</v>
+        <v>293.2451244000001</v>
       </c>
       <c r="N80">
-        <v>-223.5091608</v>
+        <v>-227.2211244000001</v>
       </c>
       <c r="O80">
-        <v>-71.52293145600001</v>
+        <v>-72.71075980800002</v>
       </c>
       <c r="P80">
-        <v>-151.986229344</v>
+        <v>-154.510364592</v>
       </c>
       <c r="Q80">
-        <v>-151.810229344</v>
+        <v>-154.334364592</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2315896324766935</v>
+        <v>0.2404367578327265</v>
       </c>
       <c r="T80">
-        <v>2.421461734027889</v>
+        <v>2.536769435648266</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07297153784258345</v>
+        <v>0.07204784749014567</v>
       </c>
       <c r="W80">
-        <v>0.2185933113767188</v>
+        <v>0.2188111175618236</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2280360557580733</v>
+        <v>0.2251495234067052</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2233525020187133</v>
+        <v>0.2252525020187133</v>
       </c>
       <c r="C81">
-        <v>-861.4146947784845</v>
+        <v>-881.2033715968729</v>
       </c>
       <c r="D81">
-        <v>382.2033052215156</v>
+        <v>378.1566284031272</v>
       </c>
       <c r="E81">
-        <v>1139.318</v>
+        <v>1155.06</v>
       </c>
       <c r="F81">
-        <v>1243.618</v>
+        <v>1259.36</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7917,37 +7917,37 @@
         <v>66.024</v>
       </c>
       <c r="M81">
-        <v>293.2451244000001</v>
+        <v>296.9570880000001</v>
       </c>
       <c r="N81">
-        <v>-227.2211244000001</v>
+        <v>-230.9330880000001</v>
       </c>
       <c r="O81">
-        <v>-72.71075980800002</v>
+        <v>-73.89858816000002</v>
       </c>
       <c r="P81">
-        <v>-154.510364592</v>
+        <v>-157.03449984</v>
       </c>
       <c r="Q81">
-        <v>-154.334364592</v>
+        <v>-156.85849984</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2404367578327265</v>
+        <v>0.2501685957243628</v>
       </c>
       <c r="T81">
-        <v>2.536769435648266</v>
+        <v>2.663607907430679</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07204784749014567</v>
+        <v>0.07114724939651886</v>
       </c>
       <c r="W81">
-        <v>0.2188111175618236</v>
+        <v>0.2190234785923009</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2251495234067052</v>
+        <v>0.2223351543641214</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2252525020187133</v>
+        <v>0.2271525020187132</v>
       </c>
       <c r="C82">
-        <v>-881.2033715968729</v>
+        <v>-900.907255695344</v>
       </c>
       <c r="D82">
-        <v>378.1566284031272</v>
+        <v>374.1947443046561</v>
       </c>
       <c r="E82">
-        <v>1155.06</v>
+        <v>1170.802</v>
       </c>
       <c r="F82">
-        <v>1259.36</v>
+        <v>1275.102</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -7999,37 +7999,37 @@
         <v>66.024</v>
       </c>
       <c r="M82">
-        <v>296.9570880000001</v>
+        <v>300.6690516</v>
       </c>
       <c r="N82">
-        <v>-230.9330880000001</v>
+        <v>-234.6450516</v>
       </c>
       <c r="O82">
-        <v>-73.89858816000002</v>
+        <v>-75.08641651200001</v>
       </c>
       <c r="P82">
-        <v>-157.03449984</v>
+        <v>-159.558635088</v>
       </c>
       <c r="Q82">
-        <v>-156.85849984</v>
+        <v>-159.382635088</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2501685957243628</v>
+        <v>0.2609248376045925</v>
       </c>
       <c r="T82">
-        <v>2.663607907430679</v>
+        <v>2.803797797295452</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07114724939651886</v>
+        <v>0.07026888829285813</v>
       </c>
       <c r="W82">
-        <v>0.2190234785923009</v>
+        <v>0.219230596140544</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2223351543641214</v>
+        <v>0.2195902759151817</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2271525020187132</v>
+        <v>0.2290525020187133</v>
       </c>
       <c r="C83">
-        <v>-900.907255695344</v>
+        <v>-920.52898451949</v>
       </c>
       <c r="D83">
-        <v>374.1947443046561</v>
+        <v>370.3150154805101</v>
       </c>
       <c r="E83">
-        <v>1170.802</v>
+        <v>1186.544</v>
       </c>
       <c r="F83">
-        <v>1275.102</v>
+        <v>1290.844</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8081,37 +8081,37 @@
         <v>66.024</v>
       </c>
       <c r="M83">
-        <v>300.6690516</v>
+        <v>304.3810152</v>
       </c>
       <c r="N83">
-        <v>-234.6450516</v>
+        <v>-238.3570152</v>
       </c>
       <c r="O83">
-        <v>-75.08641651200001</v>
+        <v>-76.27424486400001</v>
       </c>
       <c r="P83">
-        <v>-159.558635088</v>
+        <v>-162.082770336</v>
       </c>
       <c r="Q83">
-        <v>-159.382635088</v>
+        <v>-161.906770336</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2609248376045925</v>
+        <v>0.2728762174715143</v>
       </c>
       <c r="T83">
-        <v>2.803797797295452</v>
+        <v>2.959564341589644</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07026888829285813</v>
+        <v>0.0694119506307501</v>
       </c>
       <c r="W83">
-        <v>0.219230596140544</v>
+        <v>0.2194326620412691</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2195902759151817</v>
+        <v>0.2169123457210941</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2290525020187133</v>
+        <v>0.2309525020187133</v>
       </c>
       <c r="C84">
-        <v>-920.52898451949</v>
+        <v>-940.0710872550279</v>
       </c>
       <c r="D84">
-        <v>370.3150154805101</v>
+        <v>366.5149127449723</v>
       </c>
       <c r="E84">
-        <v>1186.544</v>
+        <v>1202.286</v>
       </c>
       <c r="F84">
-        <v>1290.844</v>
+        <v>1306.586</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8163,37 +8163,37 @@
         <v>66.024</v>
       </c>
       <c r="M84">
-        <v>304.3810152</v>
+        <v>308.0929788000001</v>
       </c>
       <c r="N84">
-        <v>-238.3570152</v>
+        <v>-242.0689788000001</v>
       </c>
       <c r="O84">
-        <v>-76.27424486400001</v>
+        <v>-77.46207321600002</v>
       </c>
       <c r="P84">
-        <v>-162.082770336</v>
+        <v>-164.6069055840001</v>
       </c>
       <c r="Q84">
-        <v>-161.906770336</v>
+        <v>-164.4309055840001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2728762174715143</v>
+        <v>0.2862336420286622</v>
       </c>
       <c r="T84">
-        <v>2.959564341589644</v>
+        <v>3.133656361683153</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0694119506307501</v>
+        <v>0.06857566206893383</v>
       </c>
       <c r="W84">
-        <v>0.2194326620412691</v>
+        <v>0.2196298588841454</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2169123457210941</v>
+        <v>0.2142989439654183</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2309525020187133</v>
+        <v>0.2328525020187133</v>
       </c>
       <c r="C85">
-        <v>-940.0710872550279</v>
+        <v>-959.5359903260908</v>
       </c>
       <c r="D85">
-        <v>366.5149127449723</v>
+        <v>362.7920096739095</v>
       </c>
       <c r="E85">
-        <v>1202.286</v>
+        <v>1218.028</v>
       </c>
       <c r="F85">
-        <v>1306.586</v>
+        <v>1322.328</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8245,37 +8245,37 @@
         <v>66.024</v>
       </c>
       <c r="M85">
-        <v>308.0929788000001</v>
+        <v>311.8049424000001</v>
       </c>
       <c r="N85">
-        <v>-242.0689788000001</v>
+        <v>-245.7809424000001</v>
       </c>
       <c r="O85">
-        <v>-77.46207321600002</v>
+        <v>-78.64990156800002</v>
       </c>
       <c r="P85">
-        <v>-164.6069055840001</v>
+        <v>-167.1310408320001</v>
       </c>
       <c r="Q85">
-        <v>-164.4309055840001</v>
+        <v>-166.9550408320001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2862336420286622</v>
+        <v>0.3012607446554537</v>
       </c>
       <c r="T85">
-        <v>3.133656361683153</v>
+        <v>3.32950988428835</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06857566206893383</v>
+        <v>0.06775928513954177</v>
       </c>
       <c r="W85">
-        <v>0.2196298588841454</v>
+        <v>0.2198223605640961</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2142989439654183</v>
+        <v>0.211747766061068</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2328525020187132</v>
+        <v>0.2347525020187133</v>
       </c>
       <c r="C86">
-        <v>-959.5359903260903</v>
+        <v>-978.9260225617902</v>
       </c>
       <c r="D86">
-        <v>362.7920096739097</v>
+        <v>359.1439774382097</v>
       </c>
       <c r="E86">
-        <v>1218.028</v>
+        <v>1233.77</v>
       </c>
       <c r="F86">
-        <v>1322.328</v>
+        <v>1338.07</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8327,37 +8327,37 @@
         <v>66.024</v>
       </c>
       <c r="M86">
-        <v>311.8049424</v>
+        <v>315.516906</v>
       </c>
       <c r="N86">
-        <v>-245.7809424</v>
+        <v>-249.492906</v>
       </c>
       <c r="O86">
-        <v>-78.649901568</v>
+        <v>-79.83772992</v>
       </c>
       <c r="P86">
-        <v>-167.131040832</v>
+        <v>-169.65517608</v>
       </c>
       <c r="Q86">
-        <v>-166.955040832</v>
+        <v>-169.47917608</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3012607446554535</v>
+        <v>0.3182914609658171</v>
       </c>
       <c r="T86">
-        <v>3.329509884288347</v>
+        <v>3.551477209907571</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06775928513954177</v>
+        <v>0.06696211707907658</v>
       </c>
       <c r="W86">
-        <v>0.2198223605640961</v>
+        <v>0.2200103327927538</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.211747766061068</v>
+        <v>0.2092566158721143</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2347525020187133</v>
+        <v>0.2366525020187132</v>
       </c>
       <c r="C87">
-        <v>-978.9260225617902</v>
+        <v>-998.2434200541727</v>
       </c>
       <c r="D87">
-        <v>359.1439774382097</v>
+        <v>355.5685799458274</v>
       </c>
       <c r="E87">
-        <v>1233.77</v>
+        <v>1249.512</v>
       </c>
       <c r="F87">
-        <v>1338.07</v>
+        <v>1353.812</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8409,37 +8409,37 @@
         <v>66.024</v>
       </c>
       <c r="M87">
-        <v>315.516906</v>
+        <v>319.2288696000001</v>
       </c>
       <c r="N87">
-        <v>-249.492906</v>
+        <v>-253.2048696000001</v>
       </c>
       <c r="O87">
-        <v>-79.83772992</v>
+        <v>-81.02555827200001</v>
       </c>
       <c r="P87">
-        <v>-169.65517608</v>
+        <v>-172.179311328</v>
       </c>
       <c r="Q87">
-        <v>-169.47917608</v>
+        <v>-172.0033113280001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3182914609658171</v>
+        <v>0.3377551367490897</v>
       </c>
       <c r="T87">
-        <v>3.551477209907571</v>
+        <v>3.805154153472398</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06696211707907658</v>
+        <v>0.06618348781071522</v>
       </c>
       <c r="W87">
-        <v>0.2200103327927538</v>
+        <v>0.2201939335742334</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2092566158721143</v>
+        <v>0.206823399408485</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2366525020187132</v>
+        <v>0.2385525020187133</v>
       </c>
       <c r="C88">
-        <v>-998.2434200541727</v>
+        <v>-1017.490330728855</v>
       </c>
       <c r="D88">
-        <v>355.5685799458274</v>
+        <v>352.0636692711453</v>
       </c>
       <c r="E88">
-        <v>1249.512</v>
+        <v>1265.254</v>
       </c>
       <c r="F88">
-        <v>1353.812</v>
+        <v>1369.554</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8491,37 +8491,37 @@
         <v>66.024</v>
       </c>
       <c r="M88">
-        <v>319.2288696000001</v>
+        <v>322.9408332</v>
       </c>
       <c r="N88">
-        <v>-253.2048696000001</v>
+        <v>-256.9168332</v>
       </c>
       <c r="O88">
-        <v>-81.02555827200001</v>
+        <v>-82.21338662400001</v>
       </c>
       <c r="P88">
-        <v>-172.179311328</v>
+        <v>-174.703446576</v>
       </c>
       <c r="Q88">
-        <v>-172.0033113280001</v>
+        <v>-174.527446576</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3377551367490897</v>
+        <v>0.3602132241913274</v>
       </c>
       <c r="T88">
-        <v>3.805154153472398</v>
+        <v>4.09785831912412</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06618348781071522</v>
+        <v>0.06542275806576446</v>
       </c>
       <c r="W88">
-        <v>0.2201939335742334</v>
+        <v>0.2203733136480927</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.206823399408485</v>
+        <v>0.204446118955514</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2385525020187133</v>
+        <v>0.2404525020187132</v>
       </c>
       <c r="C89">
-        <v>-1017.490330728855</v>
+        <v>-1036.668818647982</v>
       </c>
       <c r="D89">
-        <v>352.0636692711453</v>
+        <v>348.6271813520181</v>
       </c>
       <c r="E89">
-        <v>1265.254</v>
+        <v>1280.996</v>
       </c>
       <c r="F89">
-        <v>1369.554</v>
+        <v>1385.296</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8573,37 +8573,37 @@
         <v>66.024</v>
       </c>
       <c r="M89">
-        <v>322.9408332</v>
+        <v>326.6527968</v>
       </c>
       <c r="N89">
-        <v>-256.9168332</v>
+        <v>-260.6287968</v>
       </c>
       <c r="O89">
-        <v>-82.21338662400001</v>
+        <v>-83.40121497600001</v>
       </c>
       <c r="P89">
-        <v>-174.703446576</v>
+        <v>-177.227581824</v>
       </c>
       <c r="Q89">
-        <v>-174.527446576</v>
+        <v>-177.051581824</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3602132241913274</v>
+        <v>0.3864143262072714</v>
       </c>
       <c r="T89">
-        <v>4.09785831912412</v>
+        <v>4.439346512384464</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06542275806576446</v>
+        <v>0.06467931763319897</v>
       </c>
       <c r="W89">
-        <v>0.2203733136480927</v>
+        <v>0.2205486169020917</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.204446118955514</v>
+        <v>0.2021228676037468</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2404525020187132</v>
+        <v>0.2423525020187133</v>
       </c>
       <c r="C90">
-        <v>-1036.668818647982</v>
+        <v>-1055.780868063612</v>
       </c>
       <c r="D90">
-        <v>348.6271813520181</v>
+        <v>345.2571319363878</v>
       </c>
       <c r="E90">
-        <v>1280.996</v>
+        <v>1296.738</v>
       </c>
       <c r="F90">
-        <v>1385.296</v>
+        <v>1401.038</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8655,37 +8655,37 @@
         <v>66.024</v>
       </c>
       <c r="M90">
-        <v>326.6527968</v>
+        <v>330.3647604</v>
       </c>
       <c r="N90">
-        <v>-260.6287968</v>
+        <v>-264.3407604</v>
       </c>
       <c r="O90">
-        <v>-83.40121497600001</v>
+        <v>-84.589043328</v>
       </c>
       <c r="P90">
-        <v>-177.227581824</v>
+        <v>-179.751717072</v>
       </c>
       <c r="Q90">
-        <v>-177.051581824</v>
+        <v>-179.575717072</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3864143262072714</v>
+        <v>0.417379264953387</v>
       </c>
       <c r="T90">
-        <v>4.439346512384464</v>
+        <v>4.842923468055779</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06467931763319897</v>
+        <v>0.06395258372720797</v>
       </c>
       <c r="W90">
-        <v>0.2205486169020917</v>
+        <v>0.2207199807571244</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2021228676037468</v>
+        <v>0.1998518241475249</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2423525020187133</v>
+        <v>0.2442525020187133</v>
       </c>
       <c r="C91">
-        <v>-1055.780868063612</v>
+        <v>-1074.828387238257</v>
       </c>
       <c r="D91">
-        <v>345.2571319363878</v>
+        <v>341.9516127617428</v>
       </c>
       <c r="E91">
-        <v>1296.738</v>
+        <v>1312.48</v>
       </c>
       <c r="F91">
-        <v>1401.038</v>
+        <v>1416.78</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8737,37 +8737,37 @@
         <v>66.024</v>
       </c>
       <c r="M91">
-        <v>330.3647604</v>
+        <v>334.076724</v>
       </c>
       <c r="N91">
-        <v>-264.3407604</v>
+        <v>-268.052724</v>
       </c>
       <c r="O91">
-        <v>-84.589043328</v>
+        <v>-85.77687168</v>
       </c>
       <c r="P91">
-        <v>-179.751717072</v>
+        <v>-182.27585232</v>
       </c>
       <c r="Q91">
-        <v>-179.575717072</v>
+        <v>-182.09985232</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.417379264953387</v>
+        <v>0.4545371914487257</v>
       </c>
       <c r="T91">
-        <v>4.842923468055779</v>
+        <v>5.327215814861358</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06395258372720797</v>
+        <v>0.06324199946357233</v>
       </c>
       <c r="W91">
-        <v>0.2207199807571244</v>
+        <v>0.2208875365264897</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1998518241475249</v>
+        <v>0.1976312483236635</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2442525020187133</v>
+        <v>0.2461525020187132</v>
       </c>
       <c r="C92">
-        <v>-1074.828387238257</v>
+        <v>-1093.813212048035</v>
       </c>
       <c r="D92">
-        <v>341.9516127617428</v>
+        <v>338.7087879519652</v>
       </c>
       <c r="E92">
-        <v>1312.48</v>
+        <v>1328.222</v>
       </c>
       <c r="F92">
-        <v>1416.78</v>
+        <v>1432.522</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8819,37 +8819,37 @@
         <v>66.024</v>
       </c>
       <c r="M92">
-        <v>334.076724</v>
+        <v>337.7886876000001</v>
       </c>
       <c r="N92">
-        <v>-268.052724</v>
+        <v>-271.7646876000001</v>
       </c>
       <c r="O92">
-        <v>-85.77687168</v>
+        <v>-86.96470003200002</v>
       </c>
       <c r="P92">
-        <v>-182.27585232</v>
+        <v>-184.799987568</v>
       </c>
       <c r="Q92">
-        <v>-182.09985232</v>
+        <v>-184.623987568</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4545371914487257</v>
+        <v>0.4999524349430287</v>
       </c>
       <c r="T92">
-        <v>5.327215814861358</v>
+        <v>5.919128683179287</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06324199946357233</v>
+        <v>0.0625470324365001</v>
       </c>
       <c r="W92">
-        <v>0.2208875365264897</v>
+        <v>0.2210514097514733</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1976312483236635</v>
+        <v>0.1954594763640628</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2461525020187132</v>
+        <v>0.2480525020187133</v>
       </c>
       <c r="C93">
-        <v>-1093.813212048035</v>
+        <v>-1112.73710938273</v>
       </c>
       <c r="D93">
-        <v>338.7087879519652</v>
+        <v>335.5268906172701</v>
       </c>
       <c r="E93">
-        <v>1328.222</v>
+        <v>1343.964</v>
       </c>
       <c r="F93">
-        <v>1432.522</v>
+        <v>1448.264</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8901,37 +8901,37 @@
         <v>66.024</v>
       </c>
       <c r="M93">
-        <v>337.7886876000001</v>
+        <v>341.5006512</v>
       </c>
       <c r="N93">
-        <v>-271.7646876000001</v>
+        <v>-275.4766512</v>
       </c>
       <c r="O93">
-        <v>-86.96470003200002</v>
+        <v>-88.15252838400002</v>
       </c>
       <c r="P93">
-        <v>-184.799987568</v>
+        <v>-187.324122816</v>
       </c>
       <c r="Q93">
-        <v>-184.623987568</v>
+        <v>-187.148122816</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4999524349430287</v>
+        <v>0.5567214893109073</v>
       </c>
       <c r="T93">
-        <v>5.919128683179287</v>
+        <v>6.6590197685767</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0625470324365001</v>
+        <v>0.06186717338827727</v>
       </c>
       <c r="W93">
-        <v>0.2210514097514733</v>
+        <v>0.2212117205150442</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1954594763640628</v>
+        <v>0.1933349168383665</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2480525020187133</v>
+        <v>0.2499525020187132</v>
       </c>
       <c r="C94">
-        <v>-1112.73710938273</v>
+        <v>-1131.601780355993</v>
       </c>
       <c r="D94">
-        <v>335.5268906172701</v>
+        <v>332.4042196440074</v>
       </c>
       <c r="E94">
-        <v>1343.964</v>
+        <v>1359.706</v>
       </c>
       <c r="F94">
-        <v>1448.264</v>
+        <v>1464.006</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8983,37 +8983,37 @@
         <v>66.024</v>
       </c>
       <c r="M94">
-        <v>341.5006512</v>
+        <v>345.2126148</v>
       </c>
       <c r="N94">
-        <v>-275.4766512</v>
+        <v>-279.1886148</v>
       </c>
       <c r="O94">
-        <v>-88.15252838400002</v>
+        <v>-89.34035673600002</v>
       </c>
       <c r="P94">
-        <v>-187.324122816</v>
+        <v>-189.848258064</v>
       </c>
       <c r="Q94">
-        <v>-187.148122816</v>
+        <v>-189.672258064</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5567214893109073</v>
+        <v>0.6297102734981798</v>
       </c>
       <c r="T94">
-        <v>6.6590197685767</v>
+        <v>7.6103083069448</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06186717338827727</v>
+        <v>0.06120193496474741</v>
       </c>
       <c r="W94">
-        <v>0.2212117205150442</v>
+        <v>0.2213685837353126</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1933349168383665</v>
+        <v>0.1912560467648357</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2499525020187132</v>
+        <v>0.2518525020187132</v>
       </c>
       <c r="C95">
-        <v>-1131.601780355993</v>
+        <v>-1150.408863337932</v>
       </c>
       <c r="D95">
-        <v>332.4042196440074</v>
+        <v>329.3391366620679</v>
       </c>
       <c r="E95">
-        <v>1359.706</v>
+        <v>1375.448</v>
       </c>
       <c r="F95">
-        <v>1464.006</v>
+        <v>1479.748</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9065,37 +9065,37 @@
         <v>66.024</v>
       </c>
       <c r="M95">
-        <v>345.2126148</v>
+        <v>348.9245784</v>
       </c>
       <c r="N95">
-        <v>-279.1886148</v>
+        <v>-282.9005784</v>
       </c>
       <c r="O95">
-        <v>-89.34035673600002</v>
+        <v>-90.52818508800001</v>
       </c>
       <c r="P95">
-        <v>-189.848258064</v>
+        <v>-192.372393312</v>
       </c>
       <c r="Q95">
-        <v>-189.672258064</v>
+        <v>-192.196393312</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6297102734981798</v>
+        <v>0.7270286524145434</v>
       </c>
       <c r="T95">
-        <v>7.6103083069448</v>
+        <v>8.878693024768937</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06120193496474741</v>
+        <v>0.06055085055022882</v>
       </c>
       <c r="W95">
-        <v>0.2213685837353126</v>
+        <v>0.221522109440256</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1912560467648357</v>
+        <v>0.1892214079694651</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2518525020187132</v>
+        <v>0.2537525020187132</v>
       </c>
       <c r="C96">
-        <v>-1150.408863337932</v>
+        <v>-1169.159936821461</v>
       </c>
       <c r="D96">
-        <v>329.3391366620679</v>
+        <v>326.3300631785393</v>
       </c>
       <c r="E96">
-        <v>1375.448</v>
+        <v>1391.19</v>
       </c>
       <c r="F96">
-        <v>1479.748</v>
+        <v>1495.49</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9147,37 +9147,37 @@
         <v>66.024</v>
       </c>
       <c r="M96">
-        <v>348.9245784</v>
+        <v>352.6365420000001</v>
       </c>
       <c r="N96">
-        <v>-282.9005784</v>
+        <v>-286.6125420000001</v>
       </c>
       <c r="O96">
-        <v>-90.52818508800001</v>
+        <v>-91.71601344000003</v>
       </c>
       <c r="P96">
-        <v>-192.372393312</v>
+        <v>-194.89652856</v>
       </c>
       <c r="Q96">
-        <v>-192.196393312</v>
+        <v>-194.72052856</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7270286524145434</v>
+        <v>0.8632743828974524</v>
       </c>
       <c r="T96">
-        <v>8.878693024768937</v>
+        <v>10.65443162972273</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06055085055022882</v>
+        <v>0.05991347317601588</v>
       </c>
       <c r="W96">
-        <v>0.221522109440256</v>
+        <v>0.2216724030250954</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1892214079694651</v>
+        <v>0.1872296036750496</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2537525020187132</v>
+        <v>0.2556525020187133</v>
       </c>
       <c r="C97">
-        <v>-1169.159936821461</v>
+        <v>-1187.856522132929</v>
       </c>
       <c r="D97">
-        <v>326.3300631785393</v>
+        <v>323.3754778670715</v>
       </c>
       <c r="E97">
-        <v>1391.19</v>
+        <v>1406.932</v>
       </c>
       <c r="F97">
-        <v>1495.49</v>
+        <v>1511.232</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9229,37 +9229,37 @@
         <v>66.024</v>
       </c>
       <c r="M97">
-        <v>352.6365420000001</v>
+        <v>356.3485056000001</v>
       </c>
       <c r="N97">
-        <v>-286.6125420000001</v>
+        <v>-290.3245056000001</v>
       </c>
       <c r="O97">
-        <v>-91.71601344000003</v>
+        <v>-92.90384179200002</v>
       </c>
       <c r="P97">
-        <v>-194.89652856</v>
+        <v>-197.420663808</v>
       </c>
       <c r="Q97">
-        <v>-194.72052856</v>
+        <v>-197.244663808</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8632743828974524</v>
+        <v>1.067642978621816</v>
       </c>
       <c r="T97">
-        <v>10.65443162972273</v>
+        <v>13.31803953715342</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05991347317601588</v>
+        <v>0.05928937449709904</v>
       </c>
       <c r="W97">
-        <v>0.2216724030250954</v>
+        <v>0.2218195654935841</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1872296036750496</v>
+        <v>0.1852792953034346</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2556525020187133</v>
+        <v>0.2575525020187133</v>
       </c>
       <c r="C98">
-        <v>-1187.856522132928</v>
+        <v>-1206.500085996826</v>
       </c>
       <c r="D98">
-        <v>323.3754778670717</v>
+        <v>320.4739140031737</v>
       </c>
       <c r="E98">
-        <v>1406.932</v>
+        <v>1422.674</v>
       </c>
       <c r="F98">
-        <v>1511.232</v>
+        <v>1526.974</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9311,37 +9311,37 @@
         <v>66.024</v>
       </c>
       <c r="M98">
-        <v>356.3485056</v>
+        <v>360.0604692</v>
       </c>
       <c r="N98">
-        <v>-290.3245056</v>
+        <v>-294.0364692</v>
       </c>
       <c r="O98">
-        <v>-92.90384179200001</v>
+        <v>-94.09167014400001</v>
       </c>
       <c r="P98">
-        <v>-197.420663808</v>
+        <v>-199.944799056</v>
       </c>
       <c r="Q98">
-        <v>-197.244663808</v>
+        <v>-199.768799056</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.067642978621813</v>
+        <v>1.408257304829085</v>
       </c>
       <c r="T98">
-        <v>13.31803953715338</v>
+        <v>17.75738604953784</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05928937449709906</v>
+        <v>0.05867814383218051</v>
       </c>
       <c r="W98">
-        <v>0.2218195654935841</v>
+        <v>0.2219636936843719</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1852792953034346</v>
+        <v>0.1833691994755641</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2575525020187133</v>
+        <v>0.2594525020187133</v>
       </c>
       <c r="C99">
-        <v>-1206.500085996826</v>
+        <v>-1225.092042963643</v>
       </c>
       <c r="D99">
-        <v>320.4739140031737</v>
+        <v>317.6239570363573</v>
       </c>
       <c r="E99">
-        <v>1422.674</v>
+        <v>1438.416</v>
       </c>
       <c r="F99">
-        <v>1526.974</v>
+        <v>1542.716</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9393,37 +9393,37 @@
         <v>66.024</v>
       </c>
       <c r="M99">
-        <v>360.0604692</v>
+        <v>363.7724328</v>
       </c>
       <c r="N99">
-        <v>-294.0364692</v>
+        <v>-297.7484328</v>
       </c>
       <c r="O99">
-        <v>-94.09167014400001</v>
+        <v>-95.27949849600002</v>
       </c>
       <c r="P99">
-        <v>-199.944799056</v>
+        <v>-202.468934304</v>
       </c>
       <c r="Q99">
-        <v>-199.768799056</v>
+        <v>-202.292934304</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.408257304829085</v>
+        <v>2.089485957243626</v>
       </c>
       <c r="T99">
-        <v>17.75738604953784</v>
+        <v>26.63607907430676</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05867814383218051</v>
+        <v>0.05807938726246437</v>
       </c>
       <c r="W99">
-        <v>0.2219636936843719</v>
+        <v>0.2221048804835109</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1833691994755641</v>
+        <v>0.1814980851952012</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2594525020187133</v>
+        <v>0.2613525020187132</v>
       </c>
       <c r="C100">
-        <v>-1225.092042963643</v>
+        <v>-1243.633757709318</v>
       </c>
       <c r="D100">
-        <v>317.6239570363573</v>
+        <v>314.8242422906816</v>
       </c>
       <c r="E100">
-        <v>1438.416</v>
+        <v>1454.158</v>
       </c>
       <c r="F100">
-        <v>1542.716</v>
+        <v>1558.458</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9475,37 +9475,37 @@
         <v>66.024</v>
       </c>
       <c r="M100">
-        <v>363.7724328</v>
+        <v>367.4843964</v>
       </c>
       <c r="N100">
-        <v>-297.7484328</v>
+        <v>-301.4603964</v>
       </c>
       <c r="O100">
-        <v>-95.27949849600002</v>
+        <v>-96.46732684800001</v>
       </c>
       <c r="P100">
-        <v>-202.468934304</v>
+        <v>-204.993069552</v>
       </c>
       <c r="Q100">
-        <v>-202.292934304</v>
+        <v>-204.817069552</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.089485957243626</v>
+        <v>4.133171914487253</v>
       </c>
       <c r="T100">
-        <v>26.63607907430676</v>
+        <v>53.27215814861352</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05807938726246437</v>
+        <v>0.05749272678506575</v>
       </c>
       <c r="W100">
-        <v>0.2221048804835109</v>
+        <v>0.2222432150240815</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1814980851952012</v>
+        <v>0.1796647712033305</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2613525020187132</v>
-      </c>
-      <c r="C101">
-        <v>-1243.633757709318</v>
-      </c>
-      <c r="D101">
-        <v>314.8242422906816</v>
-      </c>
-      <c r="E101">
-        <v>1454.158</v>
-      </c>
-      <c r="F101">
-        <v>1558.458</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>1469.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>66.2</v>
-      </c>
-      <c r="K101">
-        <v>0.176</v>
-      </c>
-      <c r="L101">
-        <v>66.024</v>
-      </c>
-      <c r="M101">
-        <v>367.4843964</v>
-      </c>
-      <c r="N101">
-        <v>-301.4603964</v>
-      </c>
-      <c r="O101">
-        <v>-96.46732684800001</v>
-      </c>
-      <c r="P101">
-        <v>-204.993069552</v>
-      </c>
-      <c r="Q101">
-        <v>-204.817069552</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.133171914487253</v>
-      </c>
-      <c r="T101">
-        <v>53.27215814861352</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05749272678506575</v>
-      </c>
-      <c r="W101">
-        <v>0.2222432150240815</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1796647712033305</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
